--- a/research/traditional_assets/database/data/mexico/mexico_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_real_estate_general_diversified.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0820173111601267</v>
+        <v>0.08180275922664632</v>
       </c>
       <c r="C2">
-        <v>1623.482437241708</v>
+        <v>1611.796283681098</v>
       </c>
       <c r="D2">
-        <v>1582.882437241708</v>
+        <v>1588.119283681098</v>
       </c>
       <c r="E2">
-        <v>-1526.7</v>
+        <v>-1509.777</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>16.923</v>
       </c>
       <c r="G2">
         <v>40.6</v>
@@ -1445,28 +1445,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.8512268999999999</v>
       </c>
       <c r="N2">
-        <v>235.6233333333333</v>
+        <v>234.7721064333333</v>
       </c>
       <c r="O2">
-        <v>70.687</v>
+        <v>70.43163192999999</v>
       </c>
       <c r="P2">
-        <v>164.9363333333333</v>
+        <v>164.3404745033333</v>
       </c>
       <c r="Q2">
-        <v>170.1463333333333</v>
+        <v>169.5504745033333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0820173111601267</v>
+        <v>0.08227339315822861</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313372</v>
+        <v>0.5307323119301447</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>276.804378871642</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08180275922664632</v>
+        <v>0.08158820729316595</v>
       </c>
       <c r="C3">
-        <v>1611.796283681098</v>
+        <v>1600.144896560796</v>
       </c>
       <c r="D3">
-        <v>1588.119283681098</v>
+        <v>1593.390896560796</v>
       </c>
       <c r="E3">
-        <v>-1509.777</v>
+        <v>-1492.854</v>
       </c>
       <c r="F3">
-        <v>16.923</v>
+        <v>33.846</v>
       </c>
       <c r="G3">
         <v>40.6</v>
@@ -1527,28 +1527,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M3">
-        <v>0.8512268999999999</v>
+        <v>1.7024538</v>
       </c>
       <c r="N3">
-        <v>234.7721064333333</v>
+        <v>233.9208795333333</v>
       </c>
       <c r="O3">
-        <v>70.43163192999999</v>
+        <v>70.17626385999999</v>
       </c>
       <c r="P3">
-        <v>164.3404745033333</v>
+        <v>163.7446156733333</v>
       </c>
       <c r="Q3">
-        <v>169.5504745033333</v>
+        <v>168.9546156733333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08227339315822861</v>
+        <v>0.08253470131955709</v>
       </c>
       <c r="T3">
-        <v>0.5307323119301447</v>
+        <v>0.5345346640717848</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>276.804378871642</v>
+        <v>138.402189435821</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08158820729316595</v>
+        <v>0.08137365535968555</v>
       </c>
       <c r="C4">
-        <v>1600.144896560796</v>
+        <v>1588.528623245651</v>
       </c>
       <c r="D4">
-        <v>1593.390896560796</v>
+        <v>1598.697623245652</v>
       </c>
       <c r="E4">
-        <v>-1492.854</v>
+        <v>-1475.931</v>
       </c>
       <c r="F4">
-        <v>33.846</v>
+        <v>50.769</v>
       </c>
       <c r="G4">
         <v>40.6</v>
@@ -1609,28 +1609,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M4">
-        <v>1.7024538</v>
+        <v>2.5536807</v>
       </c>
       <c r="N4">
-        <v>233.9208795333333</v>
+        <v>233.0696526333333</v>
       </c>
       <c r="O4">
-        <v>70.17626385999999</v>
+        <v>69.92089579</v>
       </c>
       <c r="P4">
-        <v>163.7446156733333</v>
+        <v>163.1487568433333</v>
       </c>
       <c r="Q4">
-        <v>168.9546156733333</v>
+        <v>168.3587568433333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08253470131955709</v>
+        <v>0.08280139727802635</v>
       </c>
       <c r="T4">
-        <v>0.5345346640717848</v>
+        <v>0.5384154152266548</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>138.402189435821</v>
+        <v>92.26812629054736</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08137365535968555</v>
+        <v>0.08115910342620519</v>
       </c>
       <c r="C5">
-        <v>1588.528623245651</v>
+        <v>1576.947815743518</v>
       </c>
       <c r="D5">
-        <v>1598.697623245652</v>
+        <v>1604.039815743518</v>
       </c>
       <c r="E5">
-        <v>-1475.931</v>
+        <v>-1459.008</v>
       </c>
       <c r="F5">
-        <v>50.769</v>
+        <v>67.69199999999999</v>
       </c>
       <c r="G5">
         <v>40.6</v>
@@ -1691,28 +1691,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M5">
-        <v>2.5536807</v>
+        <v>3.4049076</v>
       </c>
       <c r="N5">
-        <v>233.0696526333333</v>
+        <v>232.2184257333333</v>
       </c>
       <c r="O5">
-        <v>69.92089579</v>
+        <v>69.66552772</v>
       </c>
       <c r="P5">
-        <v>163.1487568433333</v>
+        <v>162.5528980133333</v>
       </c>
       <c r="Q5">
-        <v>168.3587568433333</v>
+        <v>167.7628980133333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08280139727802635</v>
+        <v>0.08307364940229707</v>
       </c>
       <c r="T5">
-        <v>0.5384154152266548</v>
+        <v>0.5423770153639179</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>92.26812629054736</v>
+        <v>69.20109471791051</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08115910342620519</v>
+        <v>0.08094455149272479</v>
       </c>
       <c r="C6">
-        <v>1576.947815743518</v>
+        <v>1565.402830783091</v>
       </c>
       <c r="D6">
-        <v>1604.039815743518</v>
+        <v>1609.417830783091</v>
       </c>
       <c r="E6">
-        <v>-1459.008</v>
+        <v>-1442.085</v>
       </c>
       <c r="F6">
-        <v>67.69199999999999</v>
+        <v>84.61500000000001</v>
       </c>
       <c r="G6">
         <v>40.6</v>
@@ -1773,28 +1773,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M6">
-        <v>3.4049076</v>
+        <v>4.2561345</v>
       </c>
       <c r="N6">
-        <v>232.2184257333333</v>
+        <v>231.3671988333333</v>
       </c>
       <c r="O6">
-        <v>69.66552772</v>
+        <v>69.41015965</v>
       </c>
       <c r="P6">
-        <v>162.5528980133333</v>
+        <v>161.9570391833333</v>
       </c>
       <c r="Q6">
-        <v>167.7628980133333</v>
+        <v>167.1670391833333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08307364940229707</v>
+        <v>0.08335163315023664</v>
       </c>
       <c r="T6">
-        <v>0.5423770153639179</v>
+        <v>0.5464220176093338</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>69.20109471791051</v>
+        <v>55.36087577432841</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08094455149272479</v>
+        <v>0.08072999955924443</v>
       </c>
       <c r="C7">
-        <v>1565.402830783091</v>
+        <v>1553.894029893306</v>
       </c>
       <c r="D7">
-        <v>1609.417830783091</v>
+        <v>1614.832029893306</v>
       </c>
       <c r="E7">
-        <v>-1442.085</v>
+        <v>-1425.162</v>
       </c>
       <c r="F7">
-        <v>84.61500000000001</v>
+        <v>101.538</v>
       </c>
       <c r="G7">
         <v>40.6</v>
@@ -1855,28 +1855,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M7">
-        <v>4.2561345</v>
+        <v>5.1073614</v>
       </c>
       <c r="N7">
-        <v>231.3671988333333</v>
+        <v>230.5159719333333</v>
       </c>
       <c r="O7">
-        <v>69.41015965</v>
+        <v>69.15479157999999</v>
       </c>
       <c r="P7">
-        <v>161.9570391833333</v>
+        <v>161.3611803533333</v>
       </c>
       <c r="Q7">
-        <v>167.1670391833333</v>
+        <v>166.5711803533333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08335163315023664</v>
+        <v>0.0836355314460047</v>
       </c>
       <c r="T7">
-        <v>0.5464220176093338</v>
+        <v>0.5505530837323118</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>55.36087577432841</v>
+        <v>46.13406314527366</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08072999955924443</v>
+        <v>0.08051544762576406</v>
       </c>
       <c r="C8">
-        <v>1553.894029893306</v>
+        <v>1542.421779484363</v>
       </c>
       <c r="D8">
-        <v>1614.832029893306</v>
+        <v>1620.282779484363</v>
       </c>
       <c r="E8">
-        <v>-1425.162</v>
+        <v>-1408.239</v>
       </c>
       <c r="F8">
-        <v>101.538</v>
+        <v>118.461</v>
       </c>
       <c r="G8">
         <v>40.6</v>
@@ -1937,28 +1937,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M8">
-        <v>5.107361399999999</v>
+        <v>5.958588299999999</v>
       </c>
       <c r="N8">
-        <v>230.5159719333333</v>
+        <v>229.6647450333333</v>
       </c>
       <c r="O8">
-        <v>69.15479157999999</v>
+        <v>68.89942350999999</v>
       </c>
       <c r="P8">
-        <v>161.3611803533333</v>
+        <v>160.7653215233333</v>
       </c>
       <c r="Q8">
-        <v>166.5711803533333</v>
+        <v>165.9753215233333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0836355314460047</v>
+        <v>0.08392553508146672</v>
       </c>
       <c r="T8">
-        <v>0.5505530837323118</v>
+        <v>0.5547729899869669</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>46.13406314527367</v>
+        <v>39.54348269594887</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08051544762576404</v>
+        <v>0.08030089569228367</v>
       </c>
       <c r="C9">
-        <v>1542.421779484363</v>
+        <v>1530.986450930382</v>
       </c>
       <c r="D9">
-        <v>1620.282779484364</v>
+        <v>1625.770450930382</v>
       </c>
       <c r="E9">
-        <v>-1408.239</v>
+        <v>-1391.316</v>
       </c>
       <c r="F9">
-        <v>118.461</v>
+        <v>135.384</v>
       </c>
       <c r="G9">
         <v>40.6</v>
@@ -2019,28 +2019,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M9">
-        <v>5.958588300000001</v>
+        <v>6.809815199999999</v>
       </c>
       <c r="N9">
-        <v>229.6647450333333</v>
+        <v>228.8135181333333</v>
       </c>
       <c r="O9">
-        <v>68.89942350999999</v>
+        <v>68.64405544</v>
       </c>
       <c r="P9">
-        <v>160.7653215233333</v>
+        <v>160.1694626933333</v>
       </c>
       <c r="Q9">
-        <v>165.9753215233333</v>
+        <v>165.3794626933334</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08392553508146672</v>
+        <v>0.0842218431437866</v>
       </c>
       <c r="T9">
-        <v>0.5547729899869669</v>
+        <v>0.5590846333341144</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>39.54348269594885</v>
+        <v>34.60054735895525</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08030089569228367</v>
+        <v>0.08008634375880329</v>
       </c>
       <c r="C10">
-        <v>1530.986450930382</v>
+        <v>1519.588420653749</v>
       </c>
       <c r="D10">
-        <v>1625.770450930382</v>
+        <v>1631.295420653749</v>
       </c>
       <c r="E10">
-        <v>-1391.316</v>
+        <v>-1374.393</v>
       </c>
       <c r="F10">
-        <v>135.384</v>
+        <v>152.307</v>
       </c>
       <c r="G10">
         <v>40.6</v>
@@ -2101,28 +2101,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M10">
-        <v>6.809815199999999</v>
+        <v>7.661042099999999</v>
       </c>
       <c r="N10">
-        <v>228.8135181333333</v>
+        <v>227.9622912333333</v>
       </c>
       <c r="O10">
-        <v>68.64405544</v>
+        <v>68.38868737</v>
       </c>
       <c r="P10">
-        <v>160.1694626933333</v>
+        <v>159.5736038633333</v>
       </c>
       <c r="Q10">
-        <v>165.3794626933334</v>
+        <v>164.7836038633334</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0842218431437866</v>
+        <v>0.0845246634712124</v>
       </c>
       <c r="T10">
-        <v>0.5590846333341144</v>
+        <v>0.5634910380735068</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>34.60054735895525</v>
+        <v>30.75604209684912</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08008634375880329</v>
+        <v>0.0798717918253229</v>
       </c>
       <c r="C11">
-        <v>1519.588420653749</v>
+        <v>1508.228070211187</v>
       </c>
       <c r="D11">
-        <v>1631.295420653749</v>
+        <v>1636.858070211187</v>
       </c>
       <c r="E11">
-        <v>-1374.393</v>
+        <v>-1357.47</v>
       </c>
       <c r="F11">
-        <v>152.307</v>
+        <v>169.23</v>
       </c>
       <c r="G11">
         <v>40.6</v>
@@ -2183,28 +2183,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M11">
-        <v>7.661042099999999</v>
+        <v>8.512269</v>
       </c>
       <c r="N11">
-        <v>227.9622912333333</v>
+        <v>227.1110643333333</v>
       </c>
       <c r="O11">
-        <v>68.38868737</v>
+        <v>68.1333193</v>
       </c>
       <c r="P11">
-        <v>159.5736038633333</v>
+        <v>158.9777450333333</v>
       </c>
       <c r="Q11">
-        <v>164.7836038633334</v>
+        <v>164.1877450333334</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0845246634712124</v>
+        <v>0.08483421313924767</v>
       </c>
       <c r="T11">
-        <v>0.5634910380735068</v>
+        <v>0.5679953629182191</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>30.75604209684912</v>
+        <v>27.6804378871642</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0798717918253229</v>
+        <v>0.07965723989184254</v>
       </c>
       <c r="C12">
-        <v>1508.228070211187</v>
+        <v>1496.905786381601</v>
       </c>
       <c r="D12">
-        <v>1636.858070211187</v>
+        <v>1642.458786381601</v>
       </c>
       <c r="E12">
-        <v>-1357.47</v>
+        <v>-1340.547</v>
       </c>
       <c r="F12">
-        <v>169.23</v>
+        <v>186.153</v>
       </c>
       <c r="G12">
         <v>40.6</v>
@@ -2265,28 +2265,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M12">
-        <v>8.512269</v>
+        <v>9.363495899999998</v>
       </c>
       <c r="N12">
-        <v>227.1110643333333</v>
+        <v>226.2598374333333</v>
       </c>
       <c r="O12">
-        <v>68.1333193</v>
+        <v>67.87795122999999</v>
       </c>
       <c r="P12">
-        <v>158.9777450333333</v>
+        <v>158.3818862033334</v>
       </c>
       <c r="Q12">
-        <v>164.1877450333334</v>
+        <v>163.5918862033334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08483421313924767</v>
+        <v>0.08515071897959835</v>
       </c>
       <c r="T12">
-        <v>0.5679953629182191</v>
+        <v>0.5726009085459586</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.6804378871642</v>
+        <v>25.16403444287655</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07965723989184254</v>
+        <v>0.07944268795836214</v>
       </c>
       <c r="C13">
-        <v>1496.905786381601</v>
+        <v>1485.621961255718</v>
       </c>
       <c r="D13">
-        <v>1642.458786381601</v>
+        <v>1648.097961255718</v>
       </c>
       <c r="E13">
-        <v>-1340.547</v>
+        <v>-1323.624</v>
       </c>
       <c r="F13">
-        <v>186.153</v>
+        <v>203.076</v>
       </c>
       <c r="G13">
         <v>40.6</v>
@@ -2347,28 +2347,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M13">
-        <v>9.363495899999998</v>
+        <v>10.2147228</v>
       </c>
       <c r="N13">
-        <v>226.2598374333333</v>
+        <v>225.4086105333333</v>
       </c>
       <c r="O13">
-        <v>67.87795122999999</v>
+        <v>67.62258315999999</v>
       </c>
       <c r="P13">
-        <v>158.3818862033334</v>
+        <v>157.7860273733334</v>
       </c>
       <c r="Q13">
-        <v>163.5918862033334</v>
+        <v>162.9960273733334</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08515071897959835</v>
+        <v>0.08547441813450243</v>
       </c>
       <c r="T13">
-        <v>0.5726009085459586</v>
+        <v>0.5773111256652377</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>25.16403444287655</v>
+        <v>23.06703157263684</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07944268795836214</v>
+        <v>0.07922813602488177</v>
       </c>
       <c r="C14">
-        <v>1485.621961255718</v>
+        <v>1474.376992327594</v>
       </c>
       <c r="D14">
-        <v>1648.097961255718</v>
+        <v>1653.775992327594</v>
       </c>
       <c r="E14">
-        <v>-1323.624</v>
+        <v>-1306.701</v>
       </c>
       <c r="F14">
-        <v>203.076</v>
+        <v>219.999</v>
       </c>
       <c r="G14">
         <v>40.6</v>
@@ -2429,28 +2429,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M14">
-        <v>10.2147228</v>
+        <v>11.0659497</v>
       </c>
       <c r="N14">
-        <v>225.4086105333333</v>
+        <v>224.5573836333333</v>
       </c>
       <c r="O14">
-        <v>67.62258315999999</v>
+        <v>67.36721509</v>
       </c>
       <c r="P14">
-        <v>157.7860273733334</v>
+        <v>157.1901685433333</v>
       </c>
       <c r="Q14">
-        <v>162.9960273733334</v>
+        <v>162.4001685433333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08547441813450243</v>
+        <v>0.08580555864928938</v>
       </c>
       <c r="T14">
-        <v>0.5773111256652377</v>
+        <v>0.5821296236378334</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>23.06703157263684</v>
+        <v>21.29264452858785</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07922813602488177</v>
+        <v>0.0790135840914014</v>
       </c>
       <c r="C15">
-        <v>1474.376992327594</v>
+        <v>1463.171282588014</v>
       </c>
       <c r="D15">
-        <v>1653.775992327594</v>
+        <v>1659.493282588014</v>
       </c>
       <c r="E15">
-        <v>-1306.701</v>
+        <v>-1289.778</v>
       </c>
       <c r="F15">
-        <v>219.999</v>
+        <v>236.922</v>
       </c>
       <c r="G15">
         <v>40.6</v>
@@ -2511,28 +2511,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M15">
-        <v>11.0659497</v>
+        <v>11.9171766</v>
       </c>
       <c r="N15">
-        <v>224.5573836333333</v>
+        <v>223.7061567333333</v>
       </c>
       <c r="O15">
-        <v>67.36721509</v>
+        <v>67.11184702</v>
       </c>
       <c r="P15">
-        <v>157.1901685433333</v>
+        <v>156.5943097133333</v>
       </c>
       <c r="Q15">
-        <v>162.4001685433333</v>
+        <v>161.8043097133333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08580555864928938</v>
+        <v>0.08614440010628069</v>
       </c>
       <c r="T15">
-        <v>0.5821296236378334</v>
+        <v>0.5870601797028152</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.29264452858785</v>
+        <v>19.77174134797443</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0790135840914014</v>
+        <v>0.078799032157921</v>
       </c>
       <c r="C16">
-        <v>1463.171282588014</v>
+        <v>1452.005240619832</v>
       </c>
       <c r="D16">
-        <v>1659.493282588014</v>
+        <v>1665.250240619832</v>
       </c>
       <c r="E16">
-        <v>-1289.778</v>
+        <v>-1272.855</v>
       </c>
       <c r="F16">
-        <v>236.922</v>
+        <v>253.845</v>
       </c>
       <c r="G16">
         <v>40.6</v>
@@ -2593,28 +2593,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M16">
-        <v>11.9171766</v>
+        <v>12.7684035</v>
       </c>
       <c r="N16">
-        <v>223.7061567333333</v>
+        <v>222.8549298333333</v>
       </c>
       <c r="O16">
-        <v>67.11184702</v>
+        <v>66.85647895</v>
       </c>
       <c r="P16">
-        <v>156.5943097133333</v>
+        <v>155.9984508833333</v>
       </c>
       <c r="Q16">
-        <v>161.8043097133333</v>
+        <v>161.2084508833333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08614440010628069</v>
+        <v>0.08649121430343648</v>
       </c>
       <c r="T16">
-        <v>0.5870601797028152</v>
+        <v>0.5921067488516789</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.77174134797443</v>
+        <v>18.45362525810947</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.078799032157921</v>
+        <v>0.07858448022444062</v>
       </c>
       <c r="C17">
-        <v>1452.005240619832</v>
+        <v>1440.879280695308</v>
       </c>
       <c r="D17">
-        <v>1665.250240619832</v>
+        <v>1671.047280695308</v>
       </c>
       <c r="E17">
-        <v>-1272.855</v>
+        <v>-1255.932</v>
       </c>
       <c r="F17">
-        <v>253.845</v>
+        <v>270.768</v>
       </c>
       <c r="G17">
         <v>40.6</v>
@@ -2675,28 +2675,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M17">
-        <v>12.7684035</v>
+        <v>13.6196304</v>
       </c>
       <c r="N17">
-        <v>222.8549298333333</v>
+        <v>222.0037029333333</v>
       </c>
       <c r="O17">
-        <v>66.85647895</v>
+        <v>66.60111087999999</v>
       </c>
       <c r="P17">
-        <v>155.9984508833333</v>
+        <v>155.4025920533333</v>
       </c>
       <c r="Q17">
-        <v>161.2084508833333</v>
+        <v>160.6125920533333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08649121430343648</v>
+        <v>0.08684628598147692</v>
       </c>
       <c r="T17">
-        <v>0.5921067488516789</v>
+        <v>0.5972734744088488</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.45362525810947</v>
+        <v>17.30027367947763</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07858448022444062</v>
+        <v>0.07836992829096023</v>
       </c>
       <c r="C18">
-        <v>1440.879280695308</v>
+        <v>1429.793822875485</v>
       </c>
       <c r="D18">
-        <v>1671.047280695308</v>
+        <v>1676.884822875485</v>
       </c>
       <c r="E18">
-        <v>-1255.932</v>
+        <v>-1239.009</v>
       </c>
       <c r="F18">
-        <v>270.768</v>
+        <v>287.691</v>
       </c>
       <c r="G18">
         <v>40.6</v>
@@ -2757,28 +2757,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M18">
-        <v>13.6196304</v>
+        <v>14.4708573</v>
       </c>
       <c r="N18">
-        <v>222.0037029333333</v>
+        <v>221.1524760333333</v>
       </c>
       <c r="O18">
-        <v>66.60111087999999</v>
+        <v>66.34574280999999</v>
       </c>
       <c r="P18">
-        <v>155.4025920533333</v>
+        <v>154.8067332233333</v>
       </c>
       <c r="Q18">
-        <v>160.6125920533333</v>
+        <v>160.0167332233333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08684628598147692</v>
+        <v>0.08720991360356656</v>
       </c>
       <c r="T18">
-        <v>0.5972734744088488</v>
+        <v>0.6025646993770351</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.30027367947763</v>
+        <v>16.28261052186129</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07836992829096023</v>
+        <v>0.07815537635747986</v>
       </c>
       <c r="C19">
-        <v>1429.793822875485</v>
+        <v>1418.749293111649</v>
       </c>
       <c r="D19">
-        <v>1676.884822875485</v>
+        <v>1682.763293111649</v>
       </c>
       <c r="E19">
-        <v>-1239.009</v>
+        <v>-1222.086</v>
       </c>
       <c r="F19">
-        <v>287.691</v>
+        <v>304.614</v>
       </c>
       <c r="G19">
         <v>40.6</v>
@@ -2839,28 +2839,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M19">
-        <v>14.4708573</v>
+        <v>15.3220842</v>
       </c>
       <c r="N19">
-        <v>221.1524760333333</v>
+        <v>220.3012491333333</v>
       </c>
       <c r="O19">
-        <v>66.34574280999999</v>
+        <v>66.09037474</v>
       </c>
       <c r="P19">
-        <v>154.8067332233333</v>
+        <v>154.2108743933333</v>
       </c>
       <c r="Q19">
-        <v>160.0167332233333</v>
+        <v>159.4208743933333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08720991360356656</v>
+        <v>0.08758241019204861</v>
       </c>
       <c r="T19">
-        <v>0.6025646993770351</v>
+        <v>0.6079849786127378</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.28261052186129</v>
+        <v>15.37802104842456</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07815537635747988</v>
+        <v>0.07794082442399949</v>
       </c>
       <c r="C20">
-        <v>1418.749293111649</v>
+        <v>1407.746123348945</v>
       </c>
       <c r="D20">
-        <v>1682.763293111649</v>
+        <v>1688.683123348945</v>
       </c>
       <c r="E20">
-        <v>-1222.086</v>
+        <v>-1205.163</v>
       </c>
       <c r="F20">
-        <v>304.614</v>
+        <v>321.537</v>
       </c>
       <c r="G20">
         <v>40.6</v>
@@ -2921,28 +2921,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M20">
-        <v>15.3220842</v>
+        <v>16.1733111</v>
       </c>
       <c r="N20">
-        <v>220.3012491333333</v>
+        <v>219.4500222333333</v>
       </c>
       <c r="O20">
-        <v>66.09037474</v>
+        <v>65.83500667</v>
       </c>
       <c r="P20">
-        <v>154.2108743933333</v>
+        <v>153.6150155633333</v>
       </c>
       <c r="Q20">
-        <v>159.4208743933333</v>
+        <v>158.8250155633333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08758241019204861</v>
+        <v>0.08796410422715986</v>
       </c>
       <c r="T20">
-        <v>0.6079849786127378</v>
+        <v>0.6135390919036432</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.37802104842456</v>
+        <v>14.56865151956011</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07794082442399949</v>
+        <v>0.07772627249051911</v>
       </c>
       <c r="C21">
-        <v>1407.746123348945</v>
+        <v>1396.784751632169</v>
       </c>
       <c r="D21">
-        <v>1688.683123348945</v>
+        <v>1694.644751632169</v>
       </c>
       <c r="E21">
-        <v>-1205.163</v>
+        <v>-1188.24</v>
       </c>
       <c r="F21">
-        <v>321.537</v>
+        <v>338.46</v>
       </c>
       <c r="G21">
         <v>40.6</v>
@@ -3003,28 +3003,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M21">
-        <v>16.1733111</v>
+        <v>17.024538</v>
       </c>
       <c r="N21">
-        <v>219.4500222333333</v>
+        <v>218.5987953333333</v>
       </c>
       <c r="O21">
-        <v>65.83500667</v>
+        <v>65.5796386</v>
       </c>
       <c r="P21">
-        <v>153.6150155633333</v>
+        <v>153.0191567333333</v>
       </c>
       <c r="Q21">
-        <v>158.8250155633333</v>
+        <v>158.2291567333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08796410422715986</v>
+        <v>0.08835534061314887</v>
       </c>
       <c r="T21">
-        <v>0.6135390919036432</v>
+        <v>0.6192320580268212</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.56865151956011</v>
+        <v>13.8402189435821</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07772627249051911</v>
+        <v>0.07751172055703873</v>
       </c>
       <c r="C22">
-        <v>1396.784751632169</v>
+        <v>1385.865622213827</v>
       </c>
       <c r="D22">
-        <v>1694.644751632169</v>
+        <v>1700.648622213827</v>
       </c>
       <c r="E22">
-        <v>-1188.24</v>
+        <v>-1171.317</v>
       </c>
       <c r="F22">
-        <v>338.46</v>
+        <v>355.383</v>
       </c>
       <c r="G22">
         <v>40.6</v>
@@ -3085,28 +3085,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M22">
-        <v>17.024538</v>
+        <v>17.8757649</v>
       </c>
       <c r="N22">
-        <v>218.5987953333333</v>
+        <v>217.7475684333333</v>
       </c>
       <c r="O22">
-        <v>65.5796386</v>
+        <v>65.32427052999999</v>
       </c>
       <c r="P22">
-        <v>153.0191567333333</v>
+        <v>152.4232979033333</v>
       </c>
       <c r="Q22">
-        <v>158.2291567333333</v>
+        <v>157.6332979033333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08835534061314887</v>
+        <v>0.08875648171777054</v>
       </c>
       <c r="T22">
-        <v>0.6192320580268212</v>
+        <v>0.6250691498746368</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.8402189435821</v>
+        <v>13.18116089864962</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07751172055703873</v>
+        <v>0.07752816862355835</v>
       </c>
       <c r="C23">
-        <v>1385.865622213827</v>
+        <v>1368.480845824096</v>
       </c>
       <c r="D23">
-        <v>1700.648622213827</v>
+        <v>1700.186845824097</v>
       </c>
       <c r="E23">
-        <v>-1171.317</v>
+        <v>-1154.394</v>
       </c>
       <c r="F23">
-        <v>355.383</v>
+        <v>372.306</v>
       </c>
       <c r="G23">
         <v>40.6</v>
@@ -3167,45 +3167,45 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M23">
-        <v>17.8757649</v>
+        <v>19.2854508</v>
       </c>
       <c r="N23">
-        <v>217.7475684333333</v>
+        <v>216.3378825333333</v>
       </c>
       <c r="O23">
-        <v>65.32427052999999</v>
+        <v>64.90136475999999</v>
       </c>
       <c r="P23">
-        <v>152.4232979033333</v>
+        <v>151.4365177733333</v>
       </c>
       <c r="Q23">
-        <v>157.6332979033333</v>
+        <v>156.6465177733333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08875648171777054</v>
+        <v>0.08916790849174147</v>
       </c>
       <c r="T23">
-        <v>0.6250691498746367</v>
+        <v>0.631055910744191</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>13.18116089864962</v>
+        <v>12.21767309340435</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07752816862355835</v>
+        <v>0.07732411669007797</v>
       </c>
       <c r="C24">
-        <v>1368.480845824096</v>
+        <v>1357.304367602667</v>
       </c>
       <c r="D24">
-        <v>1700.186845824097</v>
+        <v>1705.933367602667</v>
       </c>
       <c r="E24">
-        <v>-1154.394</v>
+        <v>-1137.471</v>
       </c>
       <c r="F24">
-        <v>372.306</v>
+        <v>389.229</v>
       </c>
       <c r="G24">
         <v>40.6</v>
@@ -3249,28 +3249,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M24">
-        <v>19.2854508</v>
+        <v>20.1620622</v>
       </c>
       <c r="N24">
-        <v>216.3378825333333</v>
+        <v>215.4612711333333</v>
       </c>
       <c r="O24">
-        <v>64.90136475999999</v>
+        <v>64.63838134</v>
       </c>
       <c r="P24">
-        <v>151.4365177733333</v>
+        <v>150.8228897933333</v>
       </c>
       <c r="Q24">
-        <v>156.6465177733333</v>
+        <v>156.0328897933333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08916790849174147</v>
+        <v>0.08959002167542593</v>
       </c>
       <c r="T24">
-        <v>0.631055910744191</v>
+        <v>0.6371981718960713</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.21767309340435</v>
+        <v>11.68646991543025</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07732411669007797</v>
+        <v>0.07712006475659759</v>
       </c>
       <c r="C25">
-        <v>1357.304367602667</v>
+        <v>1346.166866867884</v>
       </c>
       <c r="D25">
-        <v>1705.933367602667</v>
+        <v>1711.718866867884</v>
       </c>
       <c r="E25">
-        <v>-1137.471</v>
+        <v>-1120.548</v>
       </c>
       <c r="F25">
-        <v>389.229</v>
+        <v>406.152</v>
       </c>
       <c r="G25">
         <v>40.6</v>
@@ -3331,28 +3331,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M25">
-        <v>20.1620622</v>
+        <v>21.0386736</v>
       </c>
       <c r="N25">
-        <v>215.4612711333333</v>
+        <v>214.5846597333333</v>
       </c>
       <c r="O25">
-        <v>64.63838134</v>
+        <v>64.37539792</v>
       </c>
       <c r="P25">
-        <v>150.8228897933333</v>
+        <v>150.2092618133333</v>
       </c>
       <c r="Q25">
-        <v>156.0328897933333</v>
+        <v>155.4192618133333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08959002167542593</v>
+        <v>0.0900232431007863</v>
       </c>
       <c r="T25">
-        <v>0.6371981718960713</v>
+        <v>0.643502071499317</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.68646991543025</v>
+        <v>11.19953366895398</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07712006475659759</v>
+        <v>0.07691601282311721</v>
       </c>
       <c r="C26">
-        <v>1346.166866867884</v>
+        <v>1335.068741533761</v>
       </c>
       <c r="D26">
-        <v>1711.718866867884</v>
+        <v>1717.543741533761</v>
       </c>
       <c r="E26">
-        <v>-1120.548</v>
+        <v>-1103.625</v>
       </c>
       <c r="F26">
-        <v>406.152</v>
+        <v>423.075</v>
       </c>
       <c r="G26">
         <v>40.6</v>
@@ -3413,28 +3413,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M26">
-        <v>21.0386736</v>
+        <v>21.915285</v>
       </c>
       <c r="N26">
-        <v>214.5846597333333</v>
+        <v>213.7080483333334</v>
       </c>
       <c r="O26">
-        <v>64.37539792</v>
+        <v>64.1124145</v>
       </c>
       <c r="P26">
-        <v>150.2092618133333</v>
+        <v>149.5956338333334</v>
       </c>
       <c r="Q26">
-        <v>155.4192618133333</v>
+        <v>154.8056338333334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0900232431007863</v>
+        <v>0.09046801709748961</v>
       </c>
       <c r="T26">
-        <v>0.643502071499317</v>
+        <v>0.6499740750919827</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.19953366895398</v>
+        <v>10.75155232219583</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07691601282311721</v>
+        <v>0.07671196088963682</v>
       </c>
       <c r="C27">
-        <v>1335.068741533761</v>
+        <v>1324.010394949112</v>
       </c>
       <c r="D27">
-        <v>1717.543741533761</v>
+        <v>1723.408394949112</v>
       </c>
       <c r="E27">
-        <v>-1103.625</v>
+        <v>-1086.702</v>
       </c>
       <c r="F27">
-        <v>423.075</v>
+        <v>439.998</v>
       </c>
       <c r="G27">
         <v>40.6</v>
@@ -3495,28 +3495,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M27">
-        <v>21.915285</v>
+        <v>22.7918964</v>
       </c>
       <c r="N27">
-        <v>213.7080483333334</v>
+        <v>212.8314369333334</v>
       </c>
       <c r="O27">
-        <v>64.1124145</v>
+        <v>63.84943108</v>
       </c>
       <c r="P27">
-        <v>149.5956338333334</v>
+        <v>148.9820058533334</v>
       </c>
       <c r="Q27">
-        <v>154.8056338333334</v>
+        <v>154.1920058533334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09046801709748961</v>
+        <v>0.09092481201302273</v>
       </c>
       <c r="T27">
-        <v>0.6499740750919827</v>
+        <v>0.6566209977006661</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.75155232219583</v>
+        <v>10.33803107903445</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07671196088963682</v>
+        <v>0.07650790895615645</v>
       </c>
       <c r="C28">
-        <v>1324.010394949112</v>
+        <v>1312.992235990661</v>
       </c>
       <c r="D28">
-        <v>1723.408394949112</v>
+        <v>1729.313235990661</v>
       </c>
       <c r="E28">
-        <v>-1086.702</v>
+        <v>-1069.779</v>
       </c>
       <c r="F28">
-        <v>439.998</v>
+        <v>456.921</v>
       </c>
       <c r="G28">
         <v>40.6</v>
@@ -3577,28 +3577,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M28">
-        <v>22.7918964</v>
+        <v>23.6685078</v>
       </c>
       <c r="N28">
-        <v>212.8314369333334</v>
+        <v>211.9548255333333</v>
       </c>
       <c r="O28">
-        <v>63.84943108</v>
+        <v>63.58644766</v>
       </c>
       <c r="P28">
-        <v>148.9820058533334</v>
+        <v>148.3683778733333</v>
       </c>
       <c r="Q28">
-        <v>154.1920058533334</v>
+        <v>153.5783778733334</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09092481201302273</v>
+        <v>0.09139412185774856</v>
       </c>
       <c r="T28">
-        <v>0.6566209977006661</v>
+        <v>0.6634500277780808</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.33803107903445</v>
+        <v>9.95514103907021</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07650790895615645</v>
+        <v>0.07663705702267605</v>
       </c>
       <c r="C29">
-        <v>1312.992235990661</v>
+        <v>1292.327267708454</v>
       </c>
       <c r="D29">
-        <v>1729.313235990661</v>
+        <v>1725.571267708454</v>
       </c>
       <c r="E29">
-        <v>-1069.779</v>
+        <v>-1052.856</v>
       </c>
       <c r="F29">
-        <v>456.921</v>
+        <v>473.8440000000001</v>
       </c>
       <c r="G29">
         <v>40.6</v>
@@ -3659,45 +3659,45 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M29">
-        <v>23.6685078</v>
+        <v>25.350654</v>
       </c>
       <c r="N29">
-        <v>211.9548255333333</v>
+        <v>210.2726793333333</v>
       </c>
       <c r="O29">
-        <v>63.58644766</v>
+        <v>63.0818038</v>
       </c>
       <c r="P29">
-        <v>148.3683778733333</v>
+        <v>147.1908755333333</v>
       </c>
       <c r="Q29">
-        <v>153.5783778733334</v>
+        <v>152.4008755333333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09139412185774856</v>
+        <v>0.09187646808705008</v>
       </c>
       <c r="T29">
-        <v>0.6634500277780808</v>
+        <v>0.6704687531354234</v>
       </c>
       <c r="U29">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>9.95514103907021</v>
+        <v>9.294566259842185</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07663705702267605</v>
+        <v>0.07644490508919567</v>
       </c>
       <c r="C30">
-        <v>1292.327267708454</v>
+        <v>1280.977621818751</v>
       </c>
       <c r="D30">
-        <v>1725.571267708454</v>
+        <v>1731.144621818751</v>
       </c>
       <c r="E30">
-        <v>-1052.856</v>
+        <v>-1035.933</v>
       </c>
       <c r="F30">
-        <v>473.8440000000001</v>
+        <v>490.7670000000001</v>
       </c>
       <c r="G30">
         <v>40.6</v>
@@ -3741,28 +3741,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M30">
-        <v>25.350654</v>
+        <v>26.2560345</v>
       </c>
       <c r="N30">
-        <v>210.2726793333333</v>
+        <v>209.3672988333333</v>
       </c>
       <c r="O30">
-        <v>63.0818038</v>
+        <v>62.81018965</v>
       </c>
       <c r="P30">
-        <v>147.1908755333333</v>
+        <v>146.5571091833334</v>
       </c>
       <c r="Q30">
-        <v>152.4008755333333</v>
+        <v>151.7671091833334</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09187646808705008</v>
+        <v>0.09237240153407843</v>
       </c>
       <c r="T30">
-        <v>0.6704687531354234</v>
+        <v>0.6776851890662126</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.294566259842185</v>
+        <v>8.974063975020041</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07644490508919567</v>
+        <v>0.07625275315571529</v>
       </c>
       <c r="C31">
-        <v>1280.977621818751</v>
+        <v>1269.664094898488</v>
       </c>
       <c r="D31">
-        <v>1731.144621818751</v>
+        <v>1736.754094898488</v>
       </c>
       <c r="E31">
-        <v>-1035.933</v>
+        <v>-1019.01</v>
       </c>
       <c r="F31">
-        <v>490.7669999999999</v>
+        <v>507.6899999999999</v>
       </c>
       <c r="G31">
         <v>40.6</v>
@@ -3823,28 +3823,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M31">
-        <v>26.25603449999999</v>
+        <v>27.16141499999999</v>
       </c>
       <c r="N31">
-        <v>209.3672988333333</v>
+        <v>208.4619183333333</v>
       </c>
       <c r="O31">
-        <v>62.81018965</v>
+        <v>62.53857549999999</v>
       </c>
       <c r="P31">
-        <v>146.5571091833334</v>
+        <v>145.9233428333333</v>
       </c>
       <c r="Q31">
-        <v>151.7671091833334</v>
+        <v>151.1333428333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09237240153407843</v>
+        <v>0.09288250450816471</v>
       </c>
       <c r="T31">
-        <v>0.6776851890662126</v>
+        <v>0.6851078088807384</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.974063975020043</v>
+        <v>8.674928509186042</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07625275315571529</v>
+        <v>0.07606060122223492</v>
       </c>
       <c r="C32">
-        <v>1269.664094898488</v>
+        <v>1258.387039200796</v>
       </c>
       <c r="D32">
-        <v>1736.754094898488</v>
+        <v>1742.400039200796</v>
       </c>
       <c r="E32">
-        <v>-1019.01</v>
+        <v>-1002.087</v>
       </c>
       <c r="F32">
-        <v>507.6899999999999</v>
+        <v>524.6129999999999</v>
       </c>
       <c r="G32">
         <v>40.6</v>
@@ -3905,28 +3905,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M32">
-        <v>27.16141499999999</v>
+        <v>28.0667955</v>
       </c>
       <c r="N32">
-        <v>208.4619183333333</v>
+        <v>207.5565378333333</v>
       </c>
       <c r="O32">
-        <v>62.53857549999999</v>
+        <v>62.26696135</v>
       </c>
       <c r="P32">
-        <v>145.9233428333333</v>
+        <v>145.2895764833333</v>
       </c>
       <c r="Q32">
-        <v>151.1333428333333</v>
+        <v>150.4995764833333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09288250450816471</v>
+        <v>0.09340739307570278</v>
       </c>
       <c r="T32">
-        <v>0.6851078088807384</v>
+        <v>0.6927455770956853</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.674928509186042</v>
+        <v>8.39509210566391</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07606060122223492</v>
+        <v>0.07586844928875452</v>
       </c>
       <c r="C33">
-        <v>1258.387039200796</v>
+        <v>1247.14681157425</v>
       </c>
       <c r="D33">
-        <v>1742.400039200796</v>
+        <v>1748.08281157425</v>
       </c>
       <c r="E33">
-        <v>-1002.087</v>
+        <v>-985.1640000000001</v>
       </c>
       <c r="F33">
-        <v>524.6129999999999</v>
+        <v>541.5359999999999</v>
       </c>
       <c r="G33">
         <v>40.6</v>
@@ -3987,28 +3987,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M33">
-        <v>28.0667955</v>
+        <v>28.972176</v>
       </c>
       <c r="N33">
-        <v>207.5565378333333</v>
+        <v>206.6511573333333</v>
       </c>
       <c r="O33">
-        <v>62.26696135</v>
+        <v>61.9953472</v>
       </c>
       <c r="P33">
-        <v>145.2895764833333</v>
+        <v>144.6558101333333</v>
       </c>
       <c r="Q33">
-        <v>150.4995764833333</v>
+        <v>149.8658101333334</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09340739307570278</v>
+        <v>0.09394771954228609</v>
       </c>
       <c r="T33">
-        <v>0.6927455770956853</v>
+        <v>0.7006079855522483</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.39509210566391</v>
+        <v>8.132745477361913</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07586844928875452</v>
+        <v>0.07567629735527415</v>
       </c>
       <c r="C34">
-        <v>1247.14681157425</v>
+        <v>1235.943773538047</v>
       </c>
       <c r="D34">
-        <v>1748.08281157425</v>
+        <v>1753.802773538047</v>
       </c>
       <c r="E34">
-        <v>-985.1640000000001</v>
+        <v>-968.241</v>
       </c>
       <c r="F34">
-        <v>541.5359999999999</v>
+        <v>558.4590000000001</v>
       </c>
       <c r="G34">
         <v>40.6</v>
@@ -4069,28 +4069,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M34">
-        <v>28.972176</v>
+        <v>29.8775565</v>
       </c>
       <c r="N34">
-        <v>206.6511573333333</v>
+        <v>205.7457768333333</v>
       </c>
       <c r="O34">
-        <v>61.9953472</v>
+        <v>61.72373305</v>
       </c>
       <c r="P34">
-        <v>144.6558101333333</v>
+        <v>144.0220437833333</v>
       </c>
       <c r="Q34">
-        <v>149.8658101333334</v>
+        <v>149.2320437833334</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09394771954228609</v>
+        <v>0.09450417515712561</v>
       </c>
       <c r="T34">
-        <v>0.7006079855522483</v>
+        <v>0.7087050927687089</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.132745477361913</v>
+        <v>7.88629864471458</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07567629735527415</v>
+        <v>0.07548414542179377</v>
       </c>
       <c r="C35">
-        <v>1235.943773538047</v>
+        <v>1224.778291358679</v>
       </c>
       <c r="D35">
-        <v>1753.802773538047</v>
+        <v>1759.560291358679</v>
       </c>
       <c r="E35">
-        <v>-968.241</v>
+        <v>-951.318</v>
       </c>
       <c r="F35">
-        <v>558.4590000000001</v>
+        <v>575.3820000000001</v>
       </c>
       <c r="G35">
         <v>40.6</v>
@@ -4151,28 +4151,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M35">
-        <v>29.8775565</v>
+        <v>30.782937</v>
       </c>
       <c r="N35">
-        <v>205.7457768333333</v>
+        <v>204.8403963333333</v>
       </c>
       <c r="O35">
-        <v>61.72373305</v>
+        <v>61.45211889999999</v>
       </c>
       <c r="P35">
-        <v>144.0220437833333</v>
+        <v>143.3882774333333</v>
       </c>
       <c r="Q35">
-        <v>149.2320437833334</v>
+        <v>148.5982774333334</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09450417515712561</v>
+        <v>0.09507749306332391</v>
       </c>
       <c r="T35">
-        <v>0.7087050927687089</v>
+        <v>0.7170475668705164</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.88629864471458</v>
+        <v>7.654348684575917</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07548414542179377</v>
+        <v>0.07548799348831338</v>
       </c>
       <c r="C36">
-        <v>1224.778291358679</v>
+        <v>1207.739619436686</v>
       </c>
       <c r="D36">
-        <v>1759.560291358679</v>
+        <v>1759.444619436686</v>
       </c>
       <c r="E36">
-        <v>-951.318</v>
+        <v>-934.395</v>
       </c>
       <c r="F36">
-        <v>575.3820000000001</v>
+        <v>592.3050000000001</v>
       </c>
       <c r="G36">
         <v>40.6</v>
@@ -4233,45 +4233,45 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M36">
-        <v>30.782937</v>
+        <v>32.1621615</v>
       </c>
       <c r="N36">
-        <v>204.8403963333333</v>
+        <v>203.4611718333333</v>
       </c>
       <c r="O36">
-        <v>61.45211889999999</v>
+        <v>61.03835155</v>
       </c>
       <c r="P36">
-        <v>143.3882774333333</v>
+        <v>142.4228202833334</v>
       </c>
       <c r="Q36">
-        <v>148.5982774333334</v>
+        <v>147.6328202833334</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09507749306332391</v>
+        <v>0.09566845152048215</v>
       </c>
       <c r="T36">
-        <v>0.7170475668705164</v>
+        <v>0.7256467324831489</v>
       </c>
       <c r="U36">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y36">
-        <v>7.654348684575917</v>
+        <v>7.326103792288131</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07548799348831338</v>
+        <v>0.07530144155483302</v>
       </c>
       <c r="C37">
-        <v>1207.739619436686</v>
+        <v>1196.441883159281</v>
       </c>
       <c r="D37">
-        <v>1759.444619436686</v>
+        <v>1765.069883159281</v>
       </c>
       <c r="E37">
-        <v>-934.395</v>
+        <v>-917.472</v>
       </c>
       <c r="F37">
-        <v>592.3050000000001</v>
+        <v>609.2280000000001</v>
       </c>
       <c r="G37">
         <v>40.6</v>
@@ -4315,28 +4315,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M37">
-        <v>32.1621615</v>
+        <v>33.0810804</v>
       </c>
       <c r="N37">
-        <v>203.4611718333333</v>
+        <v>202.5422529333333</v>
       </c>
       <c r="O37">
-        <v>61.03835155</v>
+        <v>60.76267587999999</v>
       </c>
       <c r="P37">
-        <v>142.4228202833334</v>
+        <v>141.7795770533333</v>
       </c>
       <c r="Q37">
-        <v>147.6328202833334</v>
+        <v>146.9895770533333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09566845152048215</v>
+        <v>0.0962778774294266</v>
       </c>
       <c r="T37">
-        <v>0.7256467324831489</v>
+        <v>0.7345146220211763</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.326103792288131</v>
+        <v>7.122600909169015</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07530144155483302</v>
+        <v>0.07511488962135263</v>
       </c>
       <c r="C38">
-        <v>1196.441883159281</v>
+        <v>1185.180232231085</v>
       </c>
       <c r="D38">
-        <v>1765.069883159281</v>
+        <v>1770.731232231085</v>
       </c>
       <c r="E38">
-        <v>-917.4720000000001</v>
+        <v>-900.5490000000001</v>
       </c>
       <c r="F38">
-        <v>609.228</v>
+        <v>626.151</v>
       </c>
       <c r="G38">
         <v>40.6</v>
@@ -4397,28 +4397,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M38">
-        <v>33.0810804</v>
+        <v>33.9999993</v>
       </c>
       <c r="N38">
-        <v>202.5422529333333</v>
+        <v>201.6233340333333</v>
       </c>
       <c r="O38">
-        <v>60.76267588</v>
+        <v>60.48700020999999</v>
       </c>
       <c r="P38">
-        <v>141.7795770533334</v>
+        <v>141.1363338233333</v>
       </c>
       <c r="Q38">
-        <v>146.9895770533334</v>
+        <v>146.3463338233333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0962778774294266</v>
+        <v>0.09690665019262323</v>
       </c>
       <c r="T38">
-        <v>0.7345146220211763</v>
+        <v>0.743664031861998</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.122600909169018</v>
+        <v>6.930098181894178</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07511488962135263</v>
+        <v>0.07492833768787226</v>
       </c>
       <c r="C39">
-        <v>1185.180232231085</v>
+        <v>1173.955014993746</v>
       </c>
       <c r="D39">
-        <v>1770.731232231085</v>
+        <v>1776.429014993746</v>
       </c>
       <c r="E39">
-        <v>-900.5490000000001</v>
+        <v>-883.6260000000001</v>
       </c>
       <c r="F39">
-        <v>626.151</v>
+        <v>643.074</v>
       </c>
       <c r="G39">
         <v>40.6</v>
@@ -4479,28 +4479,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M39">
-        <v>33.9999993</v>
+        <v>34.9189182</v>
       </c>
       <c r="N39">
-        <v>201.6233340333333</v>
+        <v>200.7044151333333</v>
       </c>
       <c r="O39">
-        <v>60.48700020999999</v>
+        <v>60.21132453999999</v>
       </c>
       <c r="P39">
-        <v>141.1363338233333</v>
+        <v>140.4930905933333</v>
       </c>
       <c r="Q39">
-        <v>146.3463338233333</v>
+        <v>145.7030905933333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09690665019262323</v>
+        <v>0.09755570594818107</v>
       </c>
       <c r="T39">
-        <v>0.743664031861998</v>
+        <v>0.7531085839557496</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.930098181894178</v>
+        <v>6.747727177107489</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07492833768787226</v>
+        <v>0.07474178575439187</v>
       </c>
       <c r="C40">
-        <v>1173.955014993746</v>
+        <v>1162.766584286908</v>
       </c>
       <c r="D40">
-        <v>1776.429014993746</v>
+        <v>1782.163584286908</v>
       </c>
       <c r="E40">
-        <v>-883.6260000000001</v>
+        <v>-866.7030000000001</v>
       </c>
       <c r="F40">
-        <v>643.074</v>
+        <v>659.997</v>
       </c>
       <c r="G40">
         <v>40.6</v>
@@ -4561,28 +4561,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M40">
-        <v>34.9189182</v>
+        <v>35.8378371</v>
       </c>
       <c r="N40">
-        <v>200.7044151333333</v>
+        <v>199.7854962333333</v>
       </c>
       <c r="O40">
-        <v>60.21132453999999</v>
+        <v>59.93564886999999</v>
       </c>
       <c r="P40">
-        <v>140.4930905933333</v>
+        <v>139.8498473633333</v>
       </c>
       <c r="Q40">
-        <v>145.7030905933333</v>
+        <v>145.0598473633333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09755570594818107</v>
+        <v>0.09822604222031456</v>
       </c>
       <c r="T40">
-        <v>0.7531085839557496</v>
+        <v>0.762862793495198</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.747727177107489</v>
+        <v>6.57470853154063</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07474178575439187</v>
+        <v>0.07455523382091149</v>
       </c>
       <c r="C41">
-        <v>1162.766584286908</v>
+        <v>1151.615297521033</v>
       </c>
       <c r="D41">
-        <v>1782.163584286908</v>
+        <v>1787.935297521033</v>
       </c>
       <c r="E41">
-        <v>-866.7030000000001</v>
+        <v>-849.78</v>
       </c>
       <c r="F41">
-        <v>659.997</v>
+        <v>676.9200000000001</v>
       </c>
       <c r="G41">
         <v>40.6</v>
@@ -4643,28 +4643,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M41">
-        <v>35.8378371</v>
+        <v>36.756756</v>
       </c>
       <c r="N41">
-        <v>199.7854962333333</v>
+        <v>198.8665773333333</v>
       </c>
       <c r="O41">
-        <v>59.93564886999999</v>
+        <v>59.6599732</v>
       </c>
       <c r="P41">
-        <v>139.8498473633333</v>
+        <v>139.2066041333333</v>
       </c>
       <c r="Q41">
-        <v>145.0598473633333</v>
+        <v>144.4166041333334</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09822604222031456</v>
+        <v>0.0989187230348525</v>
       </c>
       <c r="T41">
-        <v>0.762862793495198</v>
+        <v>0.772942143352628</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.57470853154063</v>
+        <v>6.410340818252115</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07455523382091149</v>
+        <v>0.07436868188743112</v>
       </c>
       <c r="C42">
-        <v>1151.615297521033</v>
+        <v>1140.501516751666</v>
       </c>
       <c r="D42">
-        <v>1787.935297521033</v>
+        <v>1793.744516751667</v>
       </c>
       <c r="E42">
-        <v>-849.78</v>
+        <v>-832.857</v>
       </c>
       <c r="F42">
-        <v>676.9200000000001</v>
+        <v>693.8430000000001</v>
       </c>
       <c r="G42">
         <v>40.6</v>
@@ -4725,28 +4725,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M42">
-        <v>36.756756</v>
+        <v>37.6756749</v>
       </c>
       <c r="N42">
-        <v>198.8665773333333</v>
+        <v>197.9476584333333</v>
       </c>
       <c r="O42">
-        <v>59.6599732</v>
+        <v>59.38429753</v>
       </c>
       <c r="P42">
-        <v>139.2066041333333</v>
+        <v>138.5633609033333</v>
       </c>
       <c r="Q42">
-        <v>144.4166041333334</v>
+        <v>143.7733609033334</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0989187230348525</v>
+        <v>0.099634884554968</v>
       </c>
       <c r="T42">
-        <v>0.772942143352628</v>
+        <v>0.783363166086581</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.410340818252115</v>
+        <v>6.253991042197185</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07436868188743112</v>
+        <v>0.07447612995395074</v>
       </c>
       <c r="C43">
-        <v>1140.501516751666</v>
+        <v>1120.227987382227</v>
       </c>
       <c r="D43">
-        <v>1793.744516751667</v>
+        <v>1790.393987382227</v>
       </c>
       <c r="E43">
-        <v>-832.857</v>
+        <v>-815.934</v>
       </c>
       <c r="F43">
-        <v>693.8430000000001</v>
+        <v>710.7660000000001</v>
       </c>
       <c r="G43">
         <v>40.6</v>
@@ -4807,45 +4807,45 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M43">
-        <v>37.6756749</v>
+        <v>39.30535980000001</v>
       </c>
       <c r="N43">
-        <v>197.9476584333333</v>
+        <v>196.3179735333333</v>
       </c>
       <c r="O43">
-        <v>59.38429753</v>
+        <v>58.89539205999999</v>
       </c>
       <c r="P43">
-        <v>138.5633609033333</v>
+        <v>137.4225814733333</v>
       </c>
       <c r="Q43">
-        <v>143.7733609033334</v>
+        <v>142.6325814733333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.099634884554968</v>
+        <v>0.1003757412999151</v>
       </c>
       <c r="T43">
-        <v>0.783363166086581</v>
+        <v>0.7941435344320495</v>
       </c>
       <c r="U43">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V43">
         <v>0.3</v>
       </c>
       <c r="W43">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>6.253991042197185</v>
+        <v>5.994687099476272</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07447612995395074</v>
+        <v>0.07429657802047038</v>
       </c>
       <c r="C44">
-        <v>1120.227987382227</v>
+        <v>1108.910955783204</v>
       </c>
       <c r="D44">
-        <v>1790.393987382227</v>
+        <v>1795.999955783204</v>
       </c>
       <c r="E44">
-        <v>-815.9340000000001</v>
+        <v>-799.0110000000001</v>
       </c>
       <c r="F44">
-        <v>710.766</v>
+        <v>727.689</v>
       </c>
       <c r="G44">
         <v>40.6</v>
@@ -4889,28 +4889,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M44">
-        <v>39.3053598</v>
+        <v>40.2412017</v>
       </c>
       <c r="N44">
-        <v>196.3179735333333</v>
+        <v>195.3821316333333</v>
       </c>
       <c r="O44">
-        <v>58.89539206</v>
+        <v>58.61463948999999</v>
       </c>
       <c r="P44">
-        <v>137.4225814733333</v>
+        <v>136.7674921433333</v>
       </c>
       <c r="Q44">
-        <v>142.6325814733333</v>
+        <v>141.9774921433333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1003757412999151</v>
+        <v>0.1011425930183691</v>
       </c>
       <c r="T44">
-        <v>0.7941435344320494</v>
+        <v>0.8053021613159557</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.994687099476274</v>
+        <v>5.855275771581477</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07429657802047038</v>
+        <v>0.07411702608698999</v>
       </c>
       <c r="C45">
-        <v>1108.910955783204</v>
+        <v>1097.629140558764</v>
       </c>
       <c r="D45">
-        <v>1795.999955783204</v>
+        <v>1801.641140558764</v>
       </c>
       <c r="E45">
-        <v>-799.0110000000001</v>
+        <v>-782.0880000000001</v>
       </c>
       <c r="F45">
-        <v>727.689</v>
+        <v>744.612</v>
       </c>
       <c r="G45">
         <v>40.6</v>
@@ -4971,28 +4971,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M45">
-        <v>40.2412017</v>
+        <v>41.1770436</v>
       </c>
       <c r="N45">
-        <v>195.3821316333333</v>
+        <v>194.4462897333333</v>
       </c>
       <c r="O45">
-        <v>58.61463948999999</v>
+        <v>58.33388692</v>
       </c>
       <c r="P45">
-        <v>136.7674921433333</v>
+        <v>136.1124028133333</v>
       </c>
       <c r="Q45">
-        <v>141.9774921433333</v>
+        <v>141.3224028133334</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1011425930183691</v>
+        <v>0.1019368322981964</v>
       </c>
       <c r="T45">
-        <v>0.8053021613159557</v>
+        <v>0.8168593105885726</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.855275771581477</v>
+        <v>5.722201322227352</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07411702608698999</v>
+        <v>0.07393747415350961</v>
       </c>
       <c r="C46">
-        <v>1097.629140558764</v>
+        <v>1086.382874595385</v>
       </c>
       <c r="D46">
-        <v>1801.641140558764</v>
+        <v>1807.317874595385</v>
       </c>
       <c r="E46">
-        <v>-782.0880000000001</v>
+        <v>-765.1650000000001</v>
       </c>
       <c r="F46">
-        <v>744.612</v>
+        <v>761.535</v>
       </c>
       <c r="G46">
         <v>40.6</v>
@@ -5053,28 +5053,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M46">
-        <v>41.1770436</v>
+        <v>42.1128855</v>
       </c>
       <c r="N46">
-        <v>194.4462897333333</v>
+        <v>193.5104478333333</v>
       </c>
       <c r="O46">
-        <v>58.33388692</v>
+        <v>58.05313434999999</v>
       </c>
       <c r="P46">
-        <v>136.1124028133333</v>
+        <v>135.4573134833333</v>
       </c>
       <c r="Q46">
-        <v>141.3224028133334</v>
+        <v>140.6673134833333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1019368322981964</v>
+        <v>0.1027599530063811</v>
       </c>
       <c r="T46">
-        <v>0.8168593105885726</v>
+        <v>0.8288367198347395</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.722201322227352</v>
+        <v>5.595041292844522</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07393747415350961</v>
+        <v>0.07375792222002923</v>
       </c>
       <c r="C47">
-        <v>1086.382874595385</v>
+        <v>1075.172494988334</v>
       </c>
       <c r="D47">
-        <v>1807.317874595385</v>
+        <v>1813.030494988334</v>
       </c>
       <c r="E47">
-        <v>-765.1650000000001</v>
+        <v>-748.2420000000001</v>
       </c>
       <c r="F47">
-        <v>761.535</v>
+        <v>778.458</v>
       </c>
       <c r="G47">
         <v>40.6</v>
@@ -5135,28 +5135,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M47">
-        <v>42.1128855</v>
+        <v>43.0487274</v>
       </c>
       <c r="N47">
-        <v>193.5104478333333</v>
+        <v>192.5746059333333</v>
       </c>
       <c r="O47">
-        <v>58.05313434999999</v>
+        <v>57.77238178</v>
       </c>
       <c r="P47">
-        <v>135.4573134833333</v>
+        <v>134.8022241533333</v>
       </c>
       <c r="Q47">
-        <v>140.6673134833333</v>
+        <v>140.0122241533333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1027599530063811</v>
+        <v>0.1036135596667208</v>
       </c>
       <c r="T47">
-        <v>0.8288367198347395</v>
+        <v>0.8412577368307642</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.595041292844522</v>
+        <v>5.473409960391381</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07375792222002923</v>
+        <v>0.07357837028654884</v>
       </c>
       <c r="C48">
-        <v>1075.172494988334</v>
+        <v>1063.998343108393</v>
       </c>
       <c r="D48">
-        <v>1813.030494988334</v>
+        <v>1818.779343108393</v>
       </c>
       <c r="E48">
-        <v>-748.2420000000001</v>
+        <v>-731.3190000000001</v>
       </c>
       <c r="F48">
-        <v>778.458</v>
+        <v>795.381</v>
       </c>
       <c r="G48">
         <v>40.6</v>
@@ -5217,28 +5217,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M48">
-        <v>43.0487274</v>
+        <v>43.9845693</v>
       </c>
       <c r="N48">
-        <v>192.5746059333333</v>
+        <v>191.6387640333333</v>
       </c>
       <c r="O48">
-        <v>57.77238178</v>
+        <v>57.49162921</v>
       </c>
       <c r="P48">
-        <v>134.8022241533333</v>
+        <v>134.1471348233333</v>
       </c>
       <c r="Q48">
-        <v>140.0122241533333</v>
+        <v>139.3571348233333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1036135596667208</v>
+        <v>0.1044993778991488</v>
       </c>
       <c r="T48">
-        <v>0.8412577368307642</v>
+        <v>0.8541474714492805</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.473409960391381</v>
+        <v>5.356954429319224</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07357837028654884</v>
+        <v>0.07339881835306847</v>
       </c>
       <c r="C49">
-        <v>1063.998343108393</v>
+        <v>1052.860764669857</v>
       </c>
       <c r="D49">
-        <v>1818.779343108393</v>
+        <v>1824.564764669857</v>
       </c>
       <c r="E49">
-        <v>-731.3190000000001</v>
+        <v>-714.396</v>
       </c>
       <c r="F49">
-        <v>795.381</v>
+        <v>812.3040000000001</v>
       </c>
       <c r="G49">
         <v>40.6</v>
@@ -5299,28 +5299,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M49">
-        <v>43.9845693</v>
+        <v>44.9204112</v>
       </c>
       <c r="N49">
-        <v>191.6387640333333</v>
+        <v>190.7029221333333</v>
       </c>
       <c r="O49">
-        <v>57.49162921</v>
+        <v>57.21087664</v>
       </c>
       <c r="P49">
-        <v>134.1471348233333</v>
+        <v>133.4920454933333</v>
       </c>
       <c r="Q49">
-        <v>139.3571348233333</v>
+        <v>138.7020454933333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1044993778991488</v>
+        <v>0.1054192660635932</v>
       </c>
       <c r="T49">
-        <v>0.8541474714492805</v>
+        <v>0.8675329650915858</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.356954429319224</v>
+        <v>5.245351212041739</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07339881835306847</v>
+        <v>0.07321926641958808</v>
       </c>
       <c r="C50">
-        <v>1052.860764669857</v>
+        <v>1041.76010979984</v>
       </c>
       <c r="D50">
-        <v>1824.564764669857</v>
+        <v>1830.387109799841</v>
       </c>
       <c r="E50">
-        <v>-714.3960000000001</v>
+        <v>-697.4730000000001</v>
       </c>
       <c r="F50">
-        <v>812.304</v>
+        <v>829.227</v>
       </c>
       <c r="G50">
         <v>40.6</v>
@@ -5381,28 +5381,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M50">
-        <v>44.9204112</v>
+        <v>45.8562531</v>
       </c>
       <c r="N50">
-        <v>190.7029221333333</v>
+        <v>189.7670802333333</v>
       </c>
       <c r="O50">
-        <v>57.21087664</v>
+        <v>56.93012407</v>
       </c>
       <c r="P50">
-        <v>133.4920454933333</v>
+        <v>132.8369561633333</v>
       </c>
       <c r="Q50">
-        <v>138.7020454933333</v>
+        <v>138.0469561633333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1054192660635932</v>
+        <v>0.1063752282737021</v>
       </c>
       <c r="T50">
-        <v>0.8675329650915858</v>
+        <v>0.8814433800531973</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.24535121204174</v>
+        <v>5.13830322812252</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07321926641958808</v>
+        <v>0.0730397144861077</v>
       </c>
       <c r="C51">
-        <v>1041.76010979984</v>
+        <v>1030.696733108909</v>
       </c>
       <c r="D51">
-        <v>1830.387109799841</v>
+        <v>1836.246733108909</v>
       </c>
       <c r="E51">
-        <v>-697.4730000000001</v>
+        <v>-680.5500000000001</v>
       </c>
       <c r="F51">
-        <v>829.227</v>
+        <v>846.15</v>
       </c>
       <c r="G51">
         <v>40.6</v>
@@ -5463,28 +5463,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M51">
-        <v>45.8562531</v>
+        <v>46.792095</v>
       </c>
       <c r="N51">
-        <v>189.7670802333333</v>
+        <v>188.8312383333333</v>
       </c>
       <c r="O51">
-        <v>56.93012407</v>
+        <v>56.64937149999999</v>
       </c>
       <c r="P51">
-        <v>132.8369561633333</v>
+        <v>132.1818668333333</v>
       </c>
       <c r="Q51">
-        <v>138.0469561633333</v>
+        <v>137.3918668333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1063752282737021</v>
+        <v>0.1073694289722154</v>
       </c>
       <c r="T51">
-        <v>0.8814433800531973</v>
+        <v>0.8959102116132733</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.13830322812252</v>
+        <v>5.035537163560069</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0730397144861077</v>
+        <v>0.07286016255262732</v>
       </c>
       <c r="C52">
-        <v>1030.696733108909</v>
+        <v>1019.670993763075</v>
       </c>
       <c r="D52">
-        <v>1836.246733108909</v>
+        <v>1842.143993763075</v>
       </c>
       <c r="E52">
-        <v>-680.5500000000001</v>
+        <v>-663.6270000000001</v>
       </c>
       <c r="F52">
-        <v>846.15</v>
+        <v>863.073</v>
       </c>
       <c r="G52">
         <v>40.6</v>
@@ -5545,28 +5545,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M52">
-        <v>46.792095</v>
+        <v>47.7279369</v>
       </c>
       <c r="N52">
-        <v>188.8312383333333</v>
+        <v>187.8953964333333</v>
       </c>
       <c r="O52">
-        <v>56.64937149999999</v>
+        <v>56.36861893</v>
       </c>
       <c r="P52">
-        <v>132.1818668333333</v>
+        <v>131.5267775033333</v>
       </c>
       <c r="Q52">
-        <v>137.3918668333333</v>
+        <v>136.7367775033333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1073694289722154</v>
+        <v>0.1084042092910762</v>
       </c>
       <c r="T52">
-        <v>0.8959102116132733</v>
+        <v>0.9109675260941688</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.035537163560069</v>
+        <v>4.936801140745166</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07286016255262732</v>
+        <v>0.07268061061914693</v>
       </c>
       <c r="C53">
-        <v>1019.670993763075</v>
+        <v>1008.683255557183</v>
       </c>
       <c r="D53">
-        <v>1842.143993763075</v>
+        <v>1848.079255557183</v>
       </c>
       <c r="E53">
-        <v>-663.6270000000001</v>
+        <v>-646.7040000000001</v>
       </c>
       <c r="F53">
-        <v>863.073</v>
+        <v>879.996</v>
       </c>
       <c r="G53">
         <v>40.6</v>
@@ -5627,28 +5627,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M53">
-        <v>47.7279369</v>
+        <v>48.6637788</v>
       </c>
       <c r="N53">
-        <v>187.8953964333333</v>
+        <v>186.9595545333333</v>
       </c>
       <c r="O53">
-        <v>56.36861893</v>
+        <v>56.08786636</v>
       </c>
       <c r="P53">
-        <v>131.5267775033333</v>
+        <v>130.8716881733334</v>
       </c>
       <c r="Q53">
-        <v>136.7367775033333</v>
+        <v>136.0816881733334</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1084042092910762</v>
+        <v>0.1094821054565561</v>
       </c>
       <c r="T53">
-        <v>0.9109675260941688</v>
+        <v>0.9266522286784347</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.936801140745166</v>
+        <v>4.841862657269298</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07268061061914693</v>
+        <v>0.07250105868566656</v>
       </c>
       <c r="C54">
-        <v>1008.683255557183</v>
+        <v>997.733886989722</v>
       </c>
       <c r="D54">
-        <v>1848.079255557183</v>
+        <v>1854.052886989722</v>
       </c>
       <c r="E54">
-        <v>-646.7040000000001</v>
+        <v>-629.7810000000001</v>
       </c>
       <c r="F54">
-        <v>879.996</v>
+        <v>896.919</v>
       </c>
       <c r="G54">
         <v>40.6</v>
@@ -5709,28 +5709,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M54">
-        <v>48.6637788</v>
+        <v>49.5996207</v>
       </c>
       <c r="N54">
-        <v>186.9595545333333</v>
+        <v>186.0237126333333</v>
       </c>
       <c r="O54">
-        <v>56.08786636</v>
+        <v>55.80711379</v>
       </c>
       <c r="P54">
-        <v>130.8716881733334</v>
+        <v>130.2165988433333</v>
       </c>
       <c r="Q54">
-        <v>136.0816881733334</v>
+        <v>135.4265988433334</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1094821054565561</v>
+        <v>0.1106058695439714</v>
       </c>
       <c r="T54">
-        <v>0.9266522286784347</v>
+        <v>0.9430043654152226</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.841862657269298</v>
+        <v>4.750506758075538</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07250105868566656</v>
+        <v>0.07232150675218618</v>
       </c>
       <c r="C55">
-        <v>997.733886989722</v>
+        <v>986.8232613390888</v>
       </c>
       <c r="D55">
-        <v>1854.052886989722</v>
+        <v>1860.065261339089</v>
       </c>
       <c r="E55">
-        <v>-629.7810000000001</v>
+        <v>-612.8580000000001</v>
       </c>
       <c r="F55">
-        <v>896.919</v>
+        <v>913.842</v>
       </c>
       <c r="G55">
         <v>40.6</v>
@@ -5791,28 +5791,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M55">
-        <v>49.5996207</v>
+        <v>50.5354626</v>
       </c>
       <c r="N55">
-        <v>186.0237126333333</v>
+        <v>185.0878707333333</v>
       </c>
       <c r="O55">
-        <v>55.80711379</v>
+        <v>55.52636121999999</v>
       </c>
       <c r="P55">
-        <v>130.2165988433333</v>
+        <v>129.5615095133333</v>
       </c>
       <c r="Q55">
-        <v>135.4265988433334</v>
+        <v>134.7715095133333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1106058695439714</v>
+        <v>0.1117784929395352</v>
       </c>
       <c r="T55">
-        <v>0.9430043654152226</v>
+        <v>0.9600674646188274</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.750506758075538</v>
+        <v>4.662534410703768</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07232150675218618</v>
+        <v>0.07214195481870581</v>
       </c>
       <c r="C56">
-        <v>986.8232613390888</v>
+        <v>975.9517567413434</v>
       </c>
       <c r="D56">
-        <v>1860.065261339089</v>
+        <v>1866.116756741344</v>
       </c>
       <c r="E56">
-        <v>-612.8580000000001</v>
+        <v>-595.9349999999999</v>
       </c>
       <c r="F56">
-        <v>913.842</v>
+        <v>930.7650000000001</v>
       </c>
       <c r="G56">
         <v>40.6</v>
@@ -5873,28 +5873,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M56">
-        <v>50.5354626</v>
+        <v>51.47130450000001</v>
       </c>
       <c r="N56">
-        <v>185.0878707333333</v>
+        <v>184.1520288333333</v>
       </c>
       <c r="O56">
-        <v>55.52636121999999</v>
+        <v>55.24560865</v>
       </c>
       <c r="P56">
-        <v>129.5615095133333</v>
+        <v>128.9064201833333</v>
       </c>
       <c r="Q56">
-        <v>134.7715095133333</v>
+        <v>134.1164201833333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1117784929395352</v>
+        <v>0.1130032329304573</v>
       </c>
       <c r="T56">
-        <v>0.9600674646188274</v>
+        <v>0.977888923787037</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.662534410703768</v>
+        <v>4.577761057781881</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07214195481870581</v>
+        <v>0.07294240288522542</v>
       </c>
       <c r="C57">
-        <v>975.9517567413434</v>
+        <v>932.3501715729637</v>
       </c>
       <c r="D57">
-        <v>1866.116756741344</v>
+        <v>1839.438171572964</v>
       </c>
       <c r="E57">
-        <v>-595.9349999999999</v>
+        <v>-579.0119999999999</v>
       </c>
       <c r="F57">
-        <v>930.7650000000001</v>
+        <v>947.6880000000001</v>
       </c>
       <c r="G57">
         <v>40.6</v>
@@ -5955,45 +5955,45 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M57">
-        <v>51.47130450000001</v>
+        <v>54.77636640000001</v>
       </c>
       <c r="N57">
-        <v>184.1520288333333</v>
+        <v>180.8469669333333</v>
       </c>
       <c r="O57">
-        <v>55.24560865</v>
+        <v>54.25409008</v>
       </c>
       <c r="P57">
-        <v>128.9064201833333</v>
+        <v>126.5928768533333</v>
       </c>
       <c r="Q57">
-        <v>134.1164201833333</v>
+        <v>131.8028768533333</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1130032329304573</v>
+        <v>0.1142836429209669</v>
       </c>
       <c r="T57">
-        <v>0.977888923787037</v>
+        <v>0.9965204492810742</v>
       </c>
       <c r="U57">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V57">
         <v>0.3</v>
       </c>
       <c r="W57">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.577761057781881</v>
+        <v>4.301550993958104</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07294240288522542</v>
+        <v>0.07278035095174504</v>
       </c>
       <c r="C58">
-        <v>932.3501715729637</v>
+        <v>920.7665295450633</v>
       </c>
       <c r="D58">
-        <v>1839.438171572964</v>
+        <v>1844.777529545064</v>
       </c>
       <c r="E58">
-        <v>-579.0119999999999</v>
+        <v>-562.0889999999999</v>
       </c>
       <c r="F58">
-        <v>947.6880000000001</v>
+        <v>964.6110000000001</v>
       </c>
       <c r="G58">
         <v>40.6</v>
@@ -6037,28 +6037,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M58">
-        <v>54.77636640000001</v>
+        <v>55.75451580000001</v>
       </c>
       <c r="N58">
-        <v>180.8469669333333</v>
+        <v>179.8688175333333</v>
       </c>
       <c r="O58">
-        <v>54.25409008</v>
+        <v>53.96064526</v>
       </c>
       <c r="P58">
-        <v>126.5928768533333</v>
+        <v>125.9081722733333</v>
       </c>
       <c r="Q58">
-        <v>131.8028768533333</v>
+        <v>131.1181722733333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1142836429209669</v>
+        <v>0.1156236068645234</v>
       </c>
       <c r="T58">
-        <v>0.9965204492810742</v>
+        <v>1.016018557356229</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.301550993958104</v>
+        <v>4.226085187046559</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07278035095174504</v>
+        <v>0.07261829901826465</v>
       </c>
       <c r="C59">
-        <v>920.7665295450633</v>
+        <v>909.213974984581</v>
       </c>
       <c r="D59">
-        <v>1844.777529545064</v>
+        <v>1850.147974984581</v>
       </c>
       <c r="E59">
-        <v>-562.0889999999999</v>
+        <v>-545.1659999999999</v>
       </c>
       <c r="F59">
-        <v>964.6110000000001</v>
+        <v>981.5340000000001</v>
       </c>
       <c r="G59">
         <v>40.6</v>
@@ -6119,28 +6119,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M59">
-        <v>55.75451580000001</v>
+        <v>56.73266520000001</v>
       </c>
       <c r="N59">
-        <v>179.8688175333333</v>
+        <v>178.8906681333333</v>
       </c>
       <c r="O59">
-        <v>53.96064526</v>
+        <v>53.66720043999999</v>
       </c>
       <c r="P59">
-        <v>125.9081722733333</v>
+        <v>125.2234676933333</v>
       </c>
       <c r="Q59">
-        <v>131.1181722733333</v>
+        <v>130.4334676933333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1156236068645234</v>
+        <v>0.1170273786149159</v>
       </c>
       <c r="T59">
-        <v>1.016018557356229</v>
+        <v>1.036445146768297</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.226085187046559</v>
+        <v>4.153221649338859</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07261829901826466</v>
+        <v>0.07245624708478428</v>
       </c>
       <c r="C60">
-        <v>909.2139749845803</v>
+        <v>897.69278018613</v>
       </c>
       <c r="D60">
-        <v>1850.14797498458</v>
+        <v>1855.54978018613</v>
       </c>
       <c r="E60">
-        <v>-545.1660000000002</v>
+        <v>-528.2430000000002</v>
       </c>
       <c r="F60">
-        <v>981.5339999999999</v>
+        <v>998.4569999999999</v>
       </c>
       <c r="G60">
         <v>40.6</v>
@@ -6201,28 +6201,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M60">
-        <v>56.7326652</v>
+        <v>57.7108146</v>
       </c>
       <c r="N60">
-        <v>178.8906681333333</v>
+        <v>177.9125187333333</v>
       </c>
       <c r="O60">
-        <v>53.66720044</v>
+        <v>53.37375562</v>
       </c>
       <c r="P60">
-        <v>125.2234676933333</v>
+        <v>124.5387631133333</v>
       </c>
       <c r="Q60">
-        <v>130.4334676933333</v>
+        <v>129.7487631133334</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1170273786149159</v>
+        <v>0.1184996270360592</v>
       </c>
       <c r="T60">
-        <v>1.036445146768296</v>
+        <v>1.057868155176074</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.15322164933886</v>
+        <v>4.08282806206193</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07245624708478428</v>
+        <v>0.07229419515130391</v>
       </c>
       <c r="C61">
-        <v>897.69278018613</v>
+        <v>886.2032206336692</v>
       </c>
       <c r="D61">
-        <v>1855.54978018613</v>
+        <v>1860.983220633669</v>
       </c>
       <c r="E61">
-        <v>-528.2430000000002</v>
+        <v>-511.3200000000002</v>
       </c>
       <c r="F61">
-        <v>998.4569999999999</v>
+        <v>1015.38</v>
       </c>
       <c r="G61">
         <v>40.6</v>
@@ -6283,28 +6283,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M61">
-        <v>57.7108146</v>
+        <v>58.688964</v>
       </c>
       <c r="N61">
-        <v>177.9125187333333</v>
+        <v>176.9343693333333</v>
       </c>
       <c r="O61">
-        <v>53.37375562</v>
+        <v>53.0803108</v>
       </c>
       <c r="P61">
-        <v>124.5387631133333</v>
+        <v>123.8540585333333</v>
       </c>
       <c r="Q61">
-        <v>129.7487631133334</v>
+        <v>129.0640585333333</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1184996270360592</v>
+        <v>0.1200454878782597</v>
       </c>
       <c r="T61">
-        <v>1.057868155176074</v>
+        <v>1.080362314004241</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.08282806206193</v>
+        <v>4.014780927694231</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07229419515130391</v>
+        <v>0.0736266432178235</v>
       </c>
       <c r="C62">
-        <v>886.2032206336692</v>
+        <v>825.527172494428</v>
       </c>
       <c r="D62">
-        <v>1860.983220633669</v>
+        <v>1817.230172494428</v>
       </c>
       <c r="E62">
-        <v>-511.3200000000002</v>
+        <v>-494.3970000000002</v>
       </c>
       <c r="F62">
-        <v>1015.38</v>
+        <v>1032.303</v>
       </c>
       <c r="G62">
         <v>40.6</v>
@@ -6365,45 +6365,45 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M62">
-        <v>58.688964</v>
+        <v>63.28017389999999</v>
       </c>
       <c r="N62">
-        <v>176.9343693333333</v>
+        <v>172.3431594333333</v>
       </c>
       <c r="O62">
-        <v>53.0803108</v>
+        <v>51.70294783</v>
       </c>
       <c r="P62">
-        <v>123.8540585333333</v>
+        <v>120.6402116033333</v>
       </c>
       <c r="Q62">
-        <v>129.0640585333333</v>
+        <v>125.8502116033333</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1200454878782597</v>
+        <v>0.1216706236354449</v>
       </c>
       <c r="T62">
-        <v>1.080362314004241</v>
+        <v>1.104010019438981</v>
       </c>
       <c r="U62">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V62">
         <v>0.3</v>
       </c>
       <c r="W62">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>4.014780927694231</v>
+        <v>3.723493770824378</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0736266432178235</v>
+        <v>0.07348909128434314</v>
       </c>
       <c r="C63">
-        <v>825.527172494428</v>
+        <v>813.0254476992573</v>
       </c>
       <c r="D63">
-        <v>1817.230172494428</v>
+        <v>1821.651447699257</v>
       </c>
       <c r="E63">
-        <v>-494.3970000000002</v>
+        <v>-477.4740000000002</v>
       </c>
       <c r="F63">
-        <v>1032.303</v>
+        <v>1049.226</v>
       </c>
       <c r="G63">
         <v>40.6</v>
@@ -6447,28 +6447,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M63">
-        <v>63.28017389999999</v>
+        <v>64.3175538</v>
       </c>
       <c r="N63">
-        <v>172.3431594333333</v>
+        <v>171.3057795333334</v>
       </c>
       <c r="O63">
-        <v>51.70294783</v>
+        <v>51.39173386</v>
       </c>
       <c r="P63">
-        <v>120.6402116033333</v>
+        <v>119.9140456733333</v>
       </c>
       <c r="Q63">
-        <v>125.8502116033333</v>
+        <v>125.1240456733333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1216706236354449</v>
+        <v>0.1233812928535346</v>
       </c>
       <c r="T63">
-        <v>1.104010019438981</v>
+        <v>1.128902340949233</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.723493770824378</v>
+        <v>3.663437419682049</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07348909128434314</v>
+        <v>0.07335153935086276</v>
       </c>
       <c r="C64">
-        <v>813.0254476992573</v>
+        <v>800.5452890763027</v>
       </c>
       <c r="D64">
-        <v>1821.651447699257</v>
+        <v>1826.094289076303</v>
       </c>
       <c r="E64">
-        <v>-477.4740000000002</v>
+        <v>-460.5510000000002</v>
       </c>
       <c r="F64">
-        <v>1049.226</v>
+        <v>1066.149</v>
       </c>
       <c r="G64">
         <v>40.6</v>
@@ -6529,28 +6529,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M64">
-        <v>64.3175538</v>
+        <v>65.35493369999999</v>
       </c>
       <c r="N64">
-        <v>171.3057795333334</v>
+        <v>170.2683996333333</v>
       </c>
       <c r="O64">
-        <v>51.39173386</v>
+        <v>51.08051989</v>
       </c>
       <c r="P64">
-        <v>119.9140456733333</v>
+        <v>119.1878797433333</v>
       </c>
       <c r="Q64">
-        <v>125.1240456733333</v>
+        <v>124.3978797433333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1233812928535346</v>
+        <v>0.1251844306780075</v>
       </c>
       <c r="T64">
-        <v>1.128902340949233</v>
+        <v>1.155140193351931</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.663437419682049</v>
+        <v>3.605287619369635</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07335153935086276</v>
+        <v>0.07321398741738237</v>
       </c>
       <c r="C65">
-        <v>800.5452890763027</v>
+        <v>788.0868548051187</v>
       </c>
       <c r="D65">
-        <v>1826.094289076303</v>
+        <v>1830.558854805119</v>
       </c>
       <c r="E65">
-        <v>-460.5510000000002</v>
+        <v>-443.6280000000002</v>
       </c>
       <c r="F65">
-        <v>1066.149</v>
+        <v>1083.072</v>
       </c>
       <c r="G65">
         <v>40.6</v>
@@ -6611,28 +6611,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M65">
-        <v>65.35493369999999</v>
+        <v>66.39231359999999</v>
       </c>
       <c r="N65">
-        <v>170.2683996333333</v>
+        <v>169.2310197333333</v>
       </c>
       <c r="O65">
-        <v>51.08051989</v>
+        <v>50.76930592</v>
       </c>
       <c r="P65">
-        <v>119.1878797433333</v>
+        <v>118.4617138133333</v>
       </c>
       <c r="Q65">
-        <v>124.3978797433333</v>
+        <v>123.6717138133333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1251844306780075</v>
+        <v>0.1270877428260622</v>
       </c>
       <c r="T65">
-        <v>1.155140193351931</v>
+        <v>1.182835704221446</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.605287619369635</v>
+        <v>3.548955000316985</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07321398741738237</v>
+        <v>0.07435043548390199</v>
       </c>
       <c r="C66">
-        <v>788.0868548051187</v>
+        <v>734.919736314331</v>
       </c>
       <c r="D66">
-        <v>1830.558854805119</v>
+        <v>1794.314736314331</v>
       </c>
       <c r="E66">
-        <v>-443.6280000000002</v>
+        <v>-426.7049999999999</v>
       </c>
       <c r="F66">
-        <v>1083.072</v>
+        <v>1099.995</v>
       </c>
       <c r="G66">
         <v>40.6</v>
@@ -6693,45 +6693,45 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M66">
-        <v>66.39231359999999</v>
+        <v>70.50967950000002</v>
       </c>
       <c r="N66">
-        <v>169.2310197333333</v>
+        <v>165.1136538333333</v>
       </c>
       <c r="O66">
-        <v>50.76930592</v>
+        <v>49.53409615</v>
       </c>
       <c r="P66">
-        <v>118.4617138133333</v>
+        <v>115.5795576833333</v>
       </c>
       <c r="Q66">
-        <v>123.6717138133333</v>
+        <v>120.7895576833333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1270877428260622</v>
+        <v>0.1290998156682914</v>
       </c>
       <c r="T66">
-        <v>1.182835704221446</v>
+        <v>1.212113815712076</v>
       </c>
       <c r="U66">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V66">
         <v>0.3</v>
       </c>
       <c r="W66">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>3.548955000316985</v>
+        <v>3.341716130383677</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07435043548390199</v>
+        <v>0.07423248355042161</v>
       </c>
       <c r="C67">
-        <v>734.919736314331</v>
+        <v>721.6916247296483</v>
       </c>
       <c r="D67">
-        <v>1794.314736314331</v>
+        <v>1798.009624729649</v>
       </c>
       <c r="E67">
-        <v>-426.7049999999999</v>
+        <v>-409.7819999999999</v>
       </c>
       <c r="F67">
-        <v>1099.995</v>
+        <v>1116.918</v>
       </c>
       <c r="G67">
         <v>40.6</v>
@@ -6775,28 +6775,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M67">
-        <v>70.50967950000002</v>
+        <v>71.59444380000001</v>
       </c>
       <c r="N67">
-        <v>165.1136538333333</v>
+        <v>164.0288895333333</v>
       </c>
       <c r="O67">
-        <v>49.53409615</v>
+        <v>49.20866685999999</v>
       </c>
       <c r="P67">
-        <v>115.5795576833333</v>
+        <v>114.8202226733333</v>
       </c>
       <c r="Q67">
-        <v>120.7895576833333</v>
+        <v>120.0302226733333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1290998156682914</v>
+        <v>0.1312302457365342</v>
       </c>
       <c r="T67">
-        <v>1.212113815712076</v>
+        <v>1.243114169055096</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.341716130383677</v>
+        <v>3.291084067802106</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07423248355042161</v>
+        <v>0.07411453161694123</v>
       </c>
       <c r="C68">
-        <v>721.6916247296483</v>
+        <v>708.4787617198299</v>
       </c>
       <c r="D68">
-        <v>1798.009624729649</v>
+        <v>1801.71976171983</v>
       </c>
       <c r="E68">
-        <v>-409.7819999999999</v>
+        <v>-392.8589999999999</v>
       </c>
       <c r="F68">
-        <v>1116.918</v>
+        <v>1133.841</v>
       </c>
       <c r="G68">
         <v>40.6</v>
@@ -6857,28 +6857,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M68">
-        <v>71.59444380000001</v>
+        <v>72.67920810000001</v>
       </c>
       <c r="N68">
-        <v>164.0288895333333</v>
+        <v>162.9441252333333</v>
       </c>
       <c r="O68">
-        <v>49.20866685999999</v>
+        <v>48.88323757</v>
       </c>
       <c r="P68">
-        <v>114.8202226733333</v>
+        <v>114.0608876633333</v>
       </c>
       <c r="Q68">
-        <v>120.0302226733333</v>
+        <v>119.2708876633333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1312302457365342</v>
+        <v>0.1334897927786098</v>
       </c>
       <c r="T68">
-        <v>1.243114169055096</v>
+        <v>1.275993331691632</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.291084067802106</v>
+        <v>3.241963410073717</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07411453161694123</v>
+        <v>0.07399657968346085</v>
       </c>
       <c r="C69">
-        <v>708.4787617198299</v>
+        <v>695.2812418749395</v>
       </c>
       <c r="D69">
-        <v>1801.71976171983</v>
+        <v>1805.44524187494</v>
       </c>
       <c r="E69">
-        <v>-392.8589999999999</v>
+        <v>-375.9359999999999</v>
       </c>
       <c r="F69">
-        <v>1133.841</v>
+        <v>1150.764</v>
       </c>
       <c r="G69">
         <v>40.6</v>
@@ -6939,28 +6939,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M69">
-        <v>72.67920810000001</v>
+        <v>73.76397240000001</v>
       </c>
       <c r="N69">
-        <v>162.9441252333333</v>
+        <v>161.8593609333333</v>
       </c>
       <c r="O69">
-        <v>48.88323757</v>
+        <v>48.55780828</v>
       </c>
       <c r="P69">
-        <v>114.0608876633333</v>
+        <v>113.3015526533333</v>
       </c>
       <c r="Q69">
-        <v>119.2708876633333</v>
+        <v>118.5115526533333</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1334897927786098</v>
+        <v>0.1358905615108152</v>
       </c>
       <c r="T69">
-        <v>1.275993331691632</v>
+        <v>1.310927441992952</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.241963410073717</v>
+        <v>3.194287477572633</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07399657968346085</v>
+        <v>0.07387862774998048</v>
       </c>
       <c r="C70">
-        <v>695.2812418749395</v>
+        <v>682.0991605690128</v>
       </c>
       <c r="D70">
-        <v>1805.44524187494</v>
+        <v>1809.186160569013</v>
       </c>
       <c r="E70">
-        <v>-375.9359999999999</v>
+        <v>-359.0129999999999</v>
       </c>
       <c r="F70">
-        <v>1150.764</v>
+        <v>1167.687</v>
       </c>
       <c r="G70">
         <v>40.6</v>
@@ -7021,28 +7021,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M70">
-        <v>73.76397240000001</v>
+        <v>74.84873670000002</v>
       </c>
       <c r="N70">
-        <v>161.8593609333333</v>
+        <v>160.7745966333333</v>
       </c>
       <c r="O70">
-        <v>48.55780828</v>
+        <v>48.23237898999999</v>
       </c>
       <c r="P70">
-        <v>113.3015526533333</v>
+        <v>112.5422176433333</v>
       </c>
       <c r="Q70">
-        <v>118.5115526533333</v>
+        <v>117.7522176433333</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1358905615108152</v>
+        <v>0.1384462185483241</v>
       </c>
       <c r="T70">
-        <v>1.310927441992952</v>
+        <v>1.348115365862098</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.194287477572633</v>
+        <v>3.147993456158536</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07387862774998048</v>
+        <v>0.07376067581650009</v>
       </c>
       <c r="C71">
-        <v>682.0991605690128</v>
+        <v>668.9326139681941</v>
       </c>
       <c r="D71">
-        <v>1809.186160569013</v>
+        <v>1812.942613968194</v>
       </c>
       <c r="E71">
-        <v>-359.0129999999999</v>
+        <v>-342.0899999999999</v>
       </c>
       <c r="F71">
-        <v>1167.687</v>
+        <v>1184.61</v>
       </c>
       <c r="G71">
         <v>40.6</v>
@@ -7103,28 +7103,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M71">
-        <v>74.84873670000002</v>
+        <v>75.93350100000001</v>
       </c>
       <c r="N71">
-        <v>160.7745966333333</v>
+        <v>159.6898323333333</v>
       </c>
       <c r="O71">
-        <v>48.23237898999999</v>
+        <v>47.9069497</v>
       </c>
       <c r="P71">
-        <v>112.5422176433333</v>
+        <v>111.7828826333333</v>
       </c>
       <c r="Q71">
-        <v>117.7522176433333</v>
+        <v>116.9928826333333</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1384462185483241</v>
+        <v>0.141172252721667</v>
       </c>
       <c r="T71">
-        <v>1.348115365862098</v>
+        <v>1.387782484655855</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.147993456158536</v>
+        <v>3.103022121070558</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07376067581650009</v>
+        <v>0.07364272388301971</v>
       </c>
       <c r="C72">
-        <v>668.9326139681941</v>
+        <v>655.7816990389756</v>
       </c>
       <c r="D72">
-        <v>1812.942613968194</v>
+        <v>1816.714699038976</v>
       </c>
       <c r="E72">
-        <v>-342.0899999999999</v>
+        <v>-325.1669999999999</v>
       </c>
       <c r="F72">
-        <v>1184.61</v>
+        <v>1201.533</v>
       </c>
       <c r="G72">
         <v>40.6</v>
@@ -7185,28 +7185,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M72">
-        <v>75.93350100000001</v>
+        <v>77.01826530000001</v>
       </c>
       <c r="N72">
-        <v>159.6898323333333</v>
+        <v>158.6050680333333</v>
       </c>
       <c r="O72">
-        <v>47.9069497</v>
+        <v>47.58152041</v>
       </c>
       <c r="P72">
-        <v>111.7828826333333</v>
+        <v>111.0235476233333</v>
       </c>
       <c r="Q72">
-        <v>116.9928826333333</v>
+        <v>116.2335476233333</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.141172252721667</v>
+        <v>0.1440862892517921</v>
       </c>
       <c r="T72">
-        <v>1.387782484655855</v>
+        <v>1.430185266814698</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.103022121070558</v>
+        <v>3.059317584154071</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07364272388301971</v>
+        <v>0.07352477194953934</v>
       </c>
       <c r="C73">
-        <v>655.7816990389758</v>
+        <v>642.6465135565436</v>
       </c>
       <c r="D73">
-        <v>1816.714699038976</v>
+        <v>1820.502513556544</v>
       </c>
       <c r="E73">
-        <v>-325.1670000000001</v>
+        <v>-308.2440000000001</v>
       </c>
       <c r="F73">
-        <v>1201.533</v>
+        <v>1218.456</v>
       </c>
       <c r="G73">
         <v>40.6</v>
@@ -7267,28 +7267,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M73">
-        <v>77.0182653</v>
+        <v>78.1030296</v>
       </c>
       <c r="N73">
-        <v>158.6050680333333</v>
+        <v>157.5203037333333</v>
       </c>
       <c r="O73">
-        <v>47.58152041</v>
+        <v>47.25609111999999</v>
       </c>
       <c r="P73">
-        <v>111.0235476233333</v>
+        <v>110.2642126133333</v>
       </c>
       <c r="Q73">
-        <v>116.2335476233333</v>
+        <v>115.4742126133333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1440862892517921</v>
+        <v>0.1472084712483548</v>
       </c>
       <c r="T73">
-        <v>1.430185266814698</v>
+        <v>1.475616819127744</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.059317584154071</v>
+        <v>3.016827062151931</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07352477194953934</v>
+        <v>0.07739262001605896</v>
       </c>
       <c r="C74">
-        <v>642.6465135565436</v>
+        <v>509.2208465720632</v>
       </c>
       <c r="D74">
-        <v>1820.502513556544</v>
+        <v>1703.999846572063</v>
       </c>
       <c r="E74">
-        <v>-308.2440000000001</v>
+        <v>-291.3210000000001</v>
       </c>
       <c r="F74">
-        <v>1218.456</v>
+        <v>1235.379</v>
       </c>
       <c r="G74">
         <v>40.6</v>
@@ -7349,45 +7349,45 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M74">
-        <v>78.1030296</v>
+        <v>88.8237501</v>
       </c>
       <c r="N74">
-        <v>157.5203037333333</v>
+        <v>146.7995832333334</v>
       </c>
       <c r="O74">
-        <v>47.25609111999999</v>
+        <v>44.03987497000001</v>
       </c>
       <c r="P74">
-        <v>110.2642126133333</v>
+        <v>102.7597082633334</v>
       </c>
       <c r="Q74">
-        <v>115.4742126133333</v>
+        <v>107.9697082633333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1472084712483548</v>
+        <v>0.1505619259854035</v>
       </c>
       <c r="T74">
-        <v>1.475616819127744</v>
+        <v>1.524413671612127</v>
       </c>
       <c r="U74">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V74">
         <v>0.3</v>
       </c>
       <c r="W74">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>3.016827062151931</v>
+        <v>2.652706433448968</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07739262001605896</v>
+        <v>0.07732926808257856</v>
       </c>
       <c r="C75">
-        <v>509.2208465720632</v>
+        <v>494.0858158831959</v>
       </c>
       <c r="D75">
-        <v>1703.999846572063</v>
+        <v>1705.787815883196</v>
       </c>
       <c r="E75">
-        <v>-291.3210000000001</v>
+        <v>-274.3980000000001</v>
       </c>
       <c r="F75">
-        <v>1235.379</v>
+        <v>1252.302</v>
       </c>
       <c r="G75">
         <v>40.6</v>
@@ -7431,28 +7431,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M75">
-        <v>88.8237501</v>
+        <v>90.0405138</v>
       </c>
       <c r="N75">
-        <v>146.7995832333334</v>
+        <v>145.5828195333333</v>
       </c>
       <c r="O75">
-        <v>44.03987497000001</v>
+        <v>43.67484586</v>
       </c>
       <c r="P75">
-        <v>102.7597082633334</v>
+        <v>101.9079736733333</v>
       </c>
       <c r="Q75">
-        <v>107.9697082633333</v>
+        <v>107.1179736733333</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1505619259854035</v>
+        <v>0.1541733387791484</v>
       </c>
       <c r="T75">
-        <v>1.524413671612127</v>
+        <v>1.576964128133771</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.652706433448968</v>
+        <v>2.61685904921317</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07732926808257856</v>
+        <v>0.0772659161490982</v>
       </c>
       <c r="C76">
-        <v>494.0858158831959</v>
+        <v>478.9545412887367</v>
       </c>
       <c r="D76">
-        <v>1705.787815883196</v>
+        <v>1707.579541288737</v>
       </c>
       <c r="E76">
-        <v>-274.3980000000001</v>
+        <v>-257.4750000000001</v>
       </c>
       <c r="F76">
-        <v>1252.302</v>
+        <v>1269.225</v>
       </c>
       <c r="G76">
         <v>40.6</v>
@@ -7513,28 +7513,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M76">
-        <v>90.0405138</v>
+        <v>91.2572775</v>
       </c>
       <c r="N76">
-        <v>145.5828195333333</v>
+        <v>144.3660558333333</v>
       </c>
       <c r="O76">
-        <v>43.67484586</v>
+        <v>43.30981675</v>
       </c>
       <c r="P76">
-        <v>101.9079736733333</v>
+        <v>101.0562390833333</v>
       </c>
       <c r="Q76">
-        <v>107.1179736733333</v>
+        <v>106.2662390833333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1541733387791484</v>
+        <v>0.1580736645963928</v>
       </c>
       <c r="T76">
-        <v>1.576964128133771</v>
+        <v>1.633718621177145</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.61685904921317</v>
+        <v>2.581967595223661</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0772659161490982</v>
+        <v>0.07720256421561782</v>
       </c>
       <c r="C77">
-        <v>478.9545412887367</v>
+        <v>463.8270346371116</v>
       </c>
       <c r="D77">
-        <v>1707.579541288737</v>
+        <v>1709.375034637112</v>
       </c>
       <c r="E77">
-        <v>-257.4750000000001</v>
+        <v>-240.5520000000001</v>
       </c>
       <c r="F77">
-        <v>1269.225</v>
+        <v>1286.148</v>
       </c>
       <c r="G77">
         <v>40.6</v>
@@ -7595,28 +7595,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M77">
-        <v>91.2572775</v>
+        <v>92.4740412</v>
       </c>
       <c r="N77">
-        <v>144.3660558333333</v>
+        <v>143.1492921333333</v>
       </c>
       <c r="O77">
-        <v>43.30981675</v>
+        <v>42.94478764</v>
       </c>
       <c r="P77">
-        <v>101.0562390833333</v>
+        <v>100.2045044933333</v>
       </c>
       <c r="Q77">
-        <v>106.2662390833333</v>
+        <v>105.4145044933333</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1580736645963928</v>
+        <v>0.1622990175650742</v>
       </c>
       <c r="T77">
-        <v>1.633718621177145</v>
+        <v>1.695202655307468</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.581967595223661</v>
+        <v>2.547994337391771</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07720256421561782</v>
+        <v>0.07713921228213744</v>
       </c>
       <c r="C78">
-        <v>463.8270346371116</v>
+        <v>448.7033078266315</v>
       </c>
       <c r="D78">
-        <v>1709.375034637112</v>
+        <v>1711.174307826632</v>
       </c>
       <c r="E78">
-        <v>-240.5520000000001</v>
+        <v>-223.6290000000001</v>
       </c>
       <c r="F78">
-        <v>1286.148</v>
+        <v>1303.071</v>
       </c>
       <c r="G78">
         <v>40.6</v>
@@ -7677,28 +7677,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M78">
-        <v>92.4740412</v>
+        <v>93.6908049</v>
       </c>
       <c r="N78">
-        <v>143.1492921333333</v>
+        <v>141.9325284333333</v>
       </c>
       <c r="O78">
-        <v>42.94478764</v>
+        <v>42.57975853</v>
       </c>
       <c r="P78">
-        <v>100.2045044933333</v>
+        <v>99.35276990333335</v>
       </c>
       <c r="Q78">
-        <v>105.4145044933333</v>
+        <v>104.5627699033333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1622990175650742</v>
+        <v>0.1668917925310323</v>
       </c>
       <c r="T78">
-        <v>1.695202655307468</v>
+        <v>1.762033127188254</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.547994337391771</v>
+        <v>2.514903501841228</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07713921228213744</v>
+        <v>0.07920526034865706</v>
       </c>
       <c r="C79">
-        <v>448.7033078266315</v>
+        <v>374.9896968842247</v>
       </c>
       <c r="D79">
-        <v>1711.174307826632</v>
+        <v>1654.383696884225</v>
       </c>
       <c r="E79">
-        <v>-223.6290000000001</v>
+        <v>-206.7060000000001</v>
       </c>
       <c r="F79">
-        <v>1303.071</v>
+        <v>1319.994</v>
       </c>
       <c r="G79">
         <v>40.6</v>
@@ -7759,45 +7759,45 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M79">
-        <v>93.6908049</v>
+        <v>100.0555452</v>
       </c>
       <c r="N79">
-        <v>141.9325284333333</v>
+        <v>135.5677881333334</v>
       </c>
       <c r="O79">
-        <v>42.57975853</v>
+        <v>40.67033644000001</v>
       </c>
       <c r="P79">
-        <v>99.35276990333335</v>
+        <v>94.89745169333335</v>
       </c>
       <c r="Q79">
-        <v>104.5627699033333</v>
+        <v>100.1074516933333</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1668917925310323</v>
+        <v>0.1719020924938957</v>
       </c>
       <c r="T79">
-        <v>1.762033127188254</v>
+        <v>1.834939096512747</v>
       </c>
       <c r="U79">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V79">
         <v>0.3</v>
       </c>
       <c r="W79">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y79">
-        <v>2.514903501841228</v>
+        <v>2.354925285373722</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07920526034865706</v>
+        <v>0.07916920841517669</v>
       </c>
       <c r="C80">
-        <v>374.9896968842247</v>
+        <v>359.0253428610072</v>
       </c>
       <c r="D80">
-        <v>1654.383696884225</v>
+        <v>1655.342342861007</v>
       </c>
       <c r="E80">
-        <v>-206.7060000000001</v>
+        <v>-189.7830000000001</v>
       </c>
       <c r="F80">
-        <v>1319.994</v>
+        <v>1336.917</v>
       </c>
       <c r="G80">
         <v>40.6</v>
@@ -7841,28 +7841,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M80">
-        <v>100.0555452</v>
+        <v>101.3383086</v>
       </c>
       <c r="N80">
-        <v>135.5677881333334</v>
+        <v>134.2850247333333</v>
       </c>
       <c r="O80">
-        <v>40.67033644000001</v>
+        <v>40.28550741999999</v>
       </c>
       <c r="P80">
-        <v>94.89745169333335</v>
+        <v>93.99951731333334</v>
       </c>
       <c r="Q80">
-        <v>100.1074516933333</v>
+        <v>99.20951731333334</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1719020924938957</v>
+        <v>0.1773895638817937</v>
       </c>
       <c r="T80">
-        <v>1.834939096512747</v>
+        <v>1.914788491487192</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.354925285373722</v>
+        <v>2.325116104546206</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07916920841517669</v>
+        <v>0.0791331564816963</v>
       </c>
       <c r="C81">
-        <v>359.0253428610072</v>
+        <v>343.0621004722216</v>
       </c>
       <c r="D81">
-        <v>1655.342342861007</v>
+        <v>1656.302100472222</v>
       </c>
       <c r="E81">
-        <v>-189.7830000000001</v>
+        <v>-172.8599999999999</v>
       </c>
       <c r="F81">
-        <v>1336.917</v>
+        <v>1353.84</v>
       </c>
       <c r="G81">
         <v>40.6</v>
@@ -7923,28 +7923,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M81">
-        <v>101.3383086</v>
+        <v>102.621072</v>
       </c>
       <c r="N81">
-        <v>134.2850247333333</v>
+        <v>133.0022613333333</v>
       </c>
       <c r="O81">
-        <v>40.28550741999999</v>
+        <v>39.90067839999999</v>
       </c>
       <c r="P81">
-        <v>93.99951731333334</v>
+        <v>93.10158293333332</v>
       </c>
       <c r="Q81">
-        <v>99.20951731333334</v>
+        <v>98.31158293333331</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1773895638817937</v>
+        <v>0.1834257824084815</v>
       </c>
       <c r="T81">
-        <v>1.914788491487192</v>
+        <v>2.002622825959082</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.325116104546206</v>
+        <v>2.296052153239378</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0791331564816963</v>
+        <v>0.07909710454821592</v>
       </c>
       <c r="C82">
-        <v>343.0621004722216</v>
+        <v>327.0999716525475</v>
       </c>
       <c r="D82">
-        <v>1656.302100472222</v>
+        <v>1657.262971652548</v>
       </c>
       <c r="E82">
-        <v>-172.8599999999999</v>
+        <v>-155.9369999999999</v>
       </c>
       <c r="F82">
-        <v>1353.84</v>
+        <v>1370.763</v>
       </c>
       <c r="G82">
         <v>40.6</v>
@@ -8005,28 +8005,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M82">
-        <v>102.621072</v>
+        <v>103.9038354</v>
       </c>
       <c r="N82">
-        <v>133.0022613333333</v>
+        <v>131.7194979333333</v>
       </c>
       <c r="O82">
-        <v>39.90067839999999</v>
+        <v>39.51584937999999</v>
       </c>
       <c r="P82">
-        <v>93.10158293333332</v>
+        <v>92.20364855333332</v>
       </c>
       <c r="Q82">
-        <v>98.31158293333331</v>
+        <v>97.41364855333332</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1834257824084815</v>
+        <v>0.1900973923590312</v>
       </c>
       <c r="T82">
-        <v>2.002622825959082</v>
+        <v>2.099702879849065</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.296052153239378</v>
+        <v>2.26770583035988</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07909710454821592</v>
+        <v>0.07906105261473553</v>
       </c>
       <c r="C83">
-        <v>327.0999716525475</v>
+        <v>311.1389583411551</v>
       </c>
       <c r="D83">
-        <v>1657.262971652548</v>
+        <v>1658.224958341155</v>
       </c>
       <c r="E83">
-        <v>-155.9369999999999</v>
+        <v>-139.0139999999999</v>
       </c>
       <c r="F83">
-        <v>1370.763</v>
+        <v>1387.686</v>
       </c>
       <c r="G83">
         <v>40.6</v>
@@ -8087,28 +8087,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M83">
-        <v>103.9038354</v>
+        <v>105.1865988</v>
       </c>
       <c r="N83">
-        <v>131.7194979333333</v>
+        <v>130.4367345333333</v>
       </c>
       <c r="O83">
-        <v>39.51584937999999</v>
+        <v>39.13102035999999</v>
       </c>
       <c r="P83">
-        <v>92.20364855333332</v>
+        <v>91.30571417333333</v>
       </c>
       <c r="Q83">
-        <v>97.41364855333332</v>
+        <v>96.51571417333332</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1900973923590312</v>
+        <v>0.1975102923040863</v>
       </c>
       <c r="T83">
-        <v>2.099702879849065</v>
+        <v>2.207569606393491</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.26770583035988</v>
+        <v>2.24005088120915</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07906105261473553</v>
+        <v>0.07902500068125515</v>
       </c>
       <c r="C84">
-        <v>311.1389583411551</v>
+        <v>295.1790624817202</v>
       </c>
       <c r="D84">
-        <v>1658.224958341155</v>
+        <v>1659.18806248172</v>
       </c>
       <c r="E84">
-        <v>-139.0139999999999</v>
+        <v>-122.0909999999999</v>
       </c>
       <c r="F84">
-        <v>1387.686</v>
+        <v>1404.609</v>
       </c>
       <c r="G84">
         <v>40.6</v>
@@ -8169,28 +8169,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M84">
-        <v>105.1865988</v>
+        <v>106.4693622</v>
       </c>
       <c r="N84">
-        <v>130.4367345333333</v>
+        <v>129.1539711333333</v>
       </c>
       <c r="O84">
-        <v>39.13102035999999</v>
+        <v>38.74619133999999</v>
       </c>
       <c r="P84">
-        <v>91.30571417333333</v>
+        <v>90.4077797933333</v>
       </c>
       <c r="Q84">
-        <v>96.51571417333332</v>
+        <v>95.6177797933333</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1975102923040863</v>
+        <v>0.2057952981250304</v>
       </c>
       <c r="T84">
-        <v>2.207569606393491</v>
+        <v>2.328126536060791</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.24005088120915</v>
+        <v>2.213062316375304</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07902500068125515</v>
+        <v>0.07898894874777479</v>
       </c>
       <c r="C85">
-        <v>295.1790624817202</v>
+        <v>279.2202860224363</v>
       </c>
       <c r="D85">
-        <v>1659.18806248172</v>
+        <v>1660.152286022437</v>
       </c>
       <c r="E85">
-        <v>-122.0909999999999</v>
+        <v>-105.1679999999999</v>
       </c>
       <c r="F85">
-        <v>1404.609</v>
+        <v>1421.532</v>
       </c>
       <c r="G85">
         <v>40.6</v>
@@ -8251,28 +8251,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M85">
-        <v>106.4693622</v>
+        <v>107.7521256</v>
       </c>
       <c r="N85">
-        <v>129.1539711333333</v>
+        <v>127.8712077333333</v>
       </c>
       <c r="O85">
-        <v>38.74619133999999</v>
+        <v>38.36136232</v>
       </c>
       <c r="P85">
-        <v>90.4077797933333</v>
+        <v>89.50984541333332</v>
       </c>
       <c r="Q85">
-        <v>95.6177797933333</v>
+        <v>94.71984541333332</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2057952981250304</v>
+        <v>0.2151159296735924</v>
       </c>
       <c r="T85">
-        <v>2.328126536060791</v>
+        <v>2.463753081936503</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.213062316375304</v>
+        <v>2.186716336418456</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07898894874777479</v>
+        <v>0.0789528968142944</v>
       </c>
       <c r="C86">
-        <v>279.2202860224365</v>
+        <v>263.2626309160305</v>
       </c>
       <c r="D86">
-        <v>1660.152286022437</v>
+        <v>1661.117630916031</v>
       </c>
       <c r="E86">
-        <v>-105.1680000000001</v>
+        <v>-88.24500000000012</v>
       </c>
       <c r="F86">
-        <v>1421.532</v>
+        <v>1438.455</v>
       </c>
       <c r="G86">
         <v>40.6</v>
@@ -8333,28 +8333,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M86">
-        <v>107.7521256</v>
+        <v>109.034889</v>
       </c>
       <c r="N86">
-        <v>127.8712077333333</v>
+        <v>126.5884443333333</v>
       </c>
       <c r="O86">
-        <v>38.36136232</v>
+        <v>37.9765333</v>
       </c>
       <c r="P86">
-        <v>89.50984541333334</v>
+        <v>88.61191103333333</v>
       </c>
       <c r="Q86">
-        <v>94.71984541333333</v>
+        <v>93.82191103333332</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2151159296735923</v>
+        <v>0.225679312095296</v>
       </c>
       <c r="T86">
-        <v>2.463753081936501</v>
+        <v>2.617463167262308</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.186716336418456</v>
+        <v>2.160990261872357</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.0789528968142944</v>
+        <v>0.07891684488081402</v>
       </c>
       <c r="C87">
-        <v>263.2626309160305</v>
+        <v>247.3060991197722</v>
       </c>
       <c r="D87">
-        <v>1661.117630916031</v>
+        <v>1662.084099119772</v>
       </c>
       <c r="E87">
-        <v>-88.24500000000012</v>
+        <v>-71.32200000000012</v>
       </c>
       <c r="F87">
-        <v>1438.455</v>
+        <v>1455.378</v>
       </c>
       <c r="G87">
         <v>40.6</v>
@@ -8415,28 +8415,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M87">
-        <v>109.034889</v>
+        <v>110.3176524</v>
       </c>
       <c r="N87">
-        <v>126.5884443333333</v>
+        <v>125.3056809333333</v>
       </c>
       <c r="O87">
-        <v>37.9765333</v>
+        <v>37.59170428</v>
       </c>
       <c r="P87">
-        <v>88.61191103333333</v>
+        <v>87.71397665333333</v>
       </c>
       <c r="Q87">
-        <v>93.82191103333332</v>
+        <v>92.92397665333333</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.225679312095296</v>
+        <v>0.2377517491486715</v>
       </c>
       <c r="T87">
-        <v>2.617463167262308</v>
+        <v>2.793131836206087</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.160990261872357</v>
+        <v>2.135862468129655</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07891684488081402</v>
+        <v>0.07888079294733363</v>
       </c>
       <c r="C88">
-        <v>247.3060991197722</v>
+        <v>231.3506925954889</v>
       </c>
       <c r="D88">
-        <v>1662.084099119772</v>
+        <v>1663.051692595489</v>
       </c>
       <c r="E88">
-        <v>-71.32200000000012</v>
+        <v>-54.39900000000011</v>
       </c>
       <c r="F88">
-        <v>1455.378</v>
+        <v>1472.301</v>
       </c>
       <c r="G88">
         <v>40.6</v>
@@ -8497,28 +8497,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M88">
-        <v>110.3176524</v>
+        <v>111.6004158</v>
       </c>
       <c r="N88">
-        <v>125.3056809333333</v>
+        <v>124.0229175333333</v>
       </c>
       <c r="O88">
-        <v>37.59170428</v>
+        <v>37.20687526</v>
       </c>
       <c r="P88">
-        <v>87.71397665333333</v>
+        <v>86.81604227333332</v>
       </c>
       <c r="Q88">
-        <v>92.92397665333333</v>
+        <v>92.02604227333332</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2377517491486715</v>
+        <v>0.2516814842102587</v>
       </c>
       <c r="T88">
-        <v>2.793131836206087</v>
+        <v>2.99582645421814</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.135862468129655</v>
+        <v>2.11131232481782</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07888079294733363</v>
+        <v>0.07884474101385325</v>
       </c>
       <c r="C89">
-        <v>231.3506925954889</v>
+        <v>215.3964133095792</v>
       </c>
       <c r="D89">
-        <v>1663.051692595489</v>
+        <v>1664.020413309579</v>
       </c>
       <c r="E89">
-        <v>-54.39900000000011</v>
+        <v>-37.47600000000011</v>
       </c>
       <c r="F89">
-        <v>1472.301</v>
+        <v>1489.224</v>
       </c>
       <c r="G89">
         <v>40.6</v>
@@ -8579,28 +8579,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M89">
-        <v>111.6004158</v>
+        <v>112.8831792</v>
       </c>
       <c r="N89">
-        <v>124.0229175333333</v>
+        <v>122.7401541333333</v>
       </c>
       <c r="O89">
-        <v>37.20687526</v>
+        <v>36.82204624</v>
       </c>
       <c r="P89">
-        <v>86.81604227333332</v>
+        <v>85.91810789333334</v>
       </c>
       <c r="Q89">
-        <v>92.02604227333332</v>
+        <v>91.12810789333334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2516814842102587</v>
+        <v>0.2679328417821105</v>
       </c>
       <c r="T89">
-        <v>2.99582645421814</v>
+        <v>3.232303508565535</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.11131232481782</v>
+        <v>2.087320139308527</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07884474101385325</v>
+        <v>0.07880868908037288</v>
       </c>
       <c r="C90">
-        <v>215.3964133095792</v>
+        <v>199.4432632330258</v>
       </c>
       <c r="D90">
-        <v>1664.020413309579</v>
+        <v>1664.990263233026</v>
       </c>
       <c r="E90">
-        <v>-37.47600000000011</v>
+        <v>-20.55300000000011</v>
       </c>
       <c r="F90">
-        <v>1489.224</v>
+        <v>1506.147</v>
       </c>
       <c r="G90">
         <v>40.6</v>
@@ -8661,28 +8661,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M90">
-        <v>112.8831792</v>
+        <v>114.1659426</v>
       </c>
       <c r="N90">
-        <v>122.7401541333333</v>
+        <v>121.4573907333333</v>
       </c>
       <c r="O90">
-        <v>36.82204624</v>
+        <v>36.43721721999999</v>
       </c>
       <c r="P90">
-        <v>85.91810789333334</v>
+        <v>85.02017351333333</v>
       </c>
       <c r="Q90">
-        <v>91.12810789333334</v>
+        <v>90.23017351333333</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2679328417821105</v>
+        <v>0.2871389916397534</v>
       </c>
       <c r="T90">
-        <v>3.232303508565535</v>
+        <v>3.511776390976093</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.087320139308527</v>
+        <v>2.063867104035396</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07880868908037288</v>
+        <v>0.0787726371468925</v>
       </c>
       <c r="C91">
-        <v>199.4432632330258</v>
+        <v>183.4912443414103</v>
       </c>
       <c r="D91">
-        <v>1664.990263233026</v>
+        <v>1665.96124434141</v>
       </c>
       <c r="E91">
-        <v>-20.55300000000011</v>
+        <v>-3.630000000000109</v>
       </c>
       <c r="F91">
-        <v>1506.147</v>
+        <v>1523.07</v>
       </c>
       <c r="G91">
         <v>40.6</v>
@@ -8743,28 +8743,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M91">
-        <v>114.1659426</v>
+        <v>115.448706</v>
       </c>
       <c r="N91">
-        <v>121.4573907333333</v>
+        <v>120.1746273333333</v>
       </c>
       <c r="O91">
-        <v>36.43721721999999</v>
+        <v>36.0523882</v>
       </c>
       <c r="P91">
-        <v>85.02017351333333</v>
+        <v>84.12223913333334</v>
       </c>
       <c r="Q91">
-        <v>90.23017351333333</v>
+        <v>89.33223913333333</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2871389916397534</v>
+        <v>0.310186371468925</v>
       </c>
       <c r="T91">
-        <v>3.511776390976093</v>
+        <v>3.847143849868762</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.063867104035396</v>
+        <v>2.040935247323892</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.0787726371468925</v>
+        <v>0.07873658521341212</v>
       </c>
       <c r="C92">
-        <v>183.4912443414103</v>
+        <v>167.5403586149253</v>
       </c>
       <c r="D92">
-        <v>1665.96124434141</v>
+        <v>1666.933358614925</v>
       </c>
       <c r="E92">
-        <v>-3.630000000000109</v>
+        <v>13.29299999999989</v>
       </c>
       <c r="F92">
-        <v>1523.07</v>
+        <v>1539.993</v>
       </c>
       <c r="G92">
         <v>40.6</v>
@@ -8825,28 +8825,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M92">
-        <v>115.448706</v>
+        <v>116.7314694</v>
       </c>
       <c r="N92">
-        <v>120.1746273333333</v>
+        <v>118.8918639333333</v>
       </c>
       <c r="O92">
-        <v>36.0523882</v>
+        <v>35.66755918</v>
       </c>
       <c r="P92">
-        <v>84.12223913333334</v>
+        <v>83.22430475333333</v>
       </c>
       <c r="Q92">
-        <v>89.33223913333333</v>
+        <v>88.43430475333332</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.310186371468925</v>
+        <v>0.3383553912601346</v>
       </c>
       <c r="T92">
-        <v>3.847143849868762</v>
+        <v>4.25703741073758</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.040935247323892</v>
+        <v>2.01850738746319</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07873658521341212</v>
+        <v>0.08784533327993174</v>
       </c>
       <c r="C93">
-        <v>167.5403586149253</v>
+        <v>-63.56071975282384</v>
       </c>
       <c r="D93">
-        <v>1666.933358614925</v>
+        <v>1452.755280247176</v>
       </c>
       <c r="E93">
-        <v>13.29299999999989</v>
+        <v>30.21599999999989</v>
       </c>
       <c r="F93">
-        <v>1539.993</v>
+        <v>1556.916</v>
       </c>
       <c r="G93">
         <v>40.6</v>
@@ -8907,45 +8907,45 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M93">
-        <v>116.7314694</v>
+        <v>140.12244</v>
       </c>
       <c r="N93">
-        <v>118.8918639333333</v>
+        <v>95.50089333333335</v>
       </c>
       <c r="O93">
-        <v>35.66755918</v>
+        <v>28.650268</v>
       </c>
       <c r="P93">
-        <v>83.22430475333333</v>
+        <v>66.85062533333334</v>
       </c>
       <c r="Q93">
-        <v>88.43430475333332</v>
+        <v>72.06062533333333</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3383553912601346</v>
+        <v>0.3735666659991469</v>
       </c>
       <c r="T93">
-        <v>4.25703741073758</v>
+        <v>4.769404361823605</v>
       </c>
       <c r="U93">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V93">
         <v>0.3</v>
       </c>
       <c r="W93">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y93">
-        <v>2.01850738746319</v>
+        <v>1.681553171164685</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08784533327993174</v>
+        <v>0.08790868134645136</v>
       </c>
       <c r="C94">
-        <v>-63.56071975282384</v>
+        <v>-81.78070792178528</v>
       </c>
       <c r="D94">
-        <v>1452.755280247176</v>
+        <v>1451.458292078215</v>
       </c>
       <c r="E94">
-        <v>30.21599999999989</v>
+        <v>47.1389999999999</v>
       </c>
       <c r="F94">
-        <v>1556.916</v>
+        <v>1573.839</v>
       </c>
       <c r="G94">
         <v>40.6</v>
@@ -8989,28 +8989,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M94">
-        <v>140.12244</v>
+        <v>141.64551</v>
       </c>
       <c r="N94">
-        <v>95.50089333333335</v>
+        <v>93.97782333333333</v>
       </c>
       <c r="O94">
-        <v>28.650268</v>
+        <v>28.193347</v>
       </c>
       <c r="P94">
-        <v>66.85062533333334</v>
+        <v>65.78447633333333</v>
       </c>
       <c r="Q94">
-        <v>72.06062533333333</v>
+        <v>70.99447633333332</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3735666659991469</v>
+        <v>0.4188383049493053</v>
       </c>
       <c r="T94">
-        <v>4.769404361823605</v>
+        <v>5.428161870362777</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.681553171164685</v>
+        <v>1.663471954270441</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08790868134645136</v>
+        <v>0.08797202941297097</v>
       </c>
       <c r="C95">
-        <v>-81.78070792178528</v>
+        <v>-99.99838231104718</v>
       </c>
       <c r="D95">
-        <v>1451.458292078215</v>
+        <v>1450.163617688953</v>
       </c>
       <c r="E95">
-        <v>47.1389999999999</v>
+        <v>64.0619999999999</v>
       </c>
       <c r="F95">
-        <v>1573.839</v>
+        <v>1590.762</v>
       </c>
       <c r="G95">
         <v>40.6</v>
@@ -9071,28 +9071,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M95">
-        <v>141.64551</v>
+        <v>143.16858</v>
       </c>
       <c r="N95">
-        <v>93.97782333333333</v>
+        <v>92.45475333333334</v>
       </c>
       <c r="O95">
-        <v>28.193347</v>
+        <v>27.736426</v>
       </c>
       <c r="P95">
-        <v>65.78447633333333</v>
+        <v>64.71832733333335</v>
       </c>
       <c r="Q95">
-        <v>70.99447633333332</v>
+        <v>69.92832733333334</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4188383049493053</v>
+        <v>0.4792004902161833</v>
       </c>
       <c r="T95">
-        <v>5.428161870362777</v>
+        <v>6.306505215081675</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.663471954270441</v>
+        <v>1.645775444118628</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08797202941297097</v>
+        <v>0.0880353774794906</v>
       </c>
       <c r="C96">
-        <v>-99.99838231104718</v>
+        <v>-118.2137491066401</v>
       </c>
       <c r="D96">
-        <v>1450.163617688953</v>
+        <v>1448.87125089336</v>
       </c>
       <c r="E96">
-        <v>64.0619999999999</v>
+        <v>80.98500000000013</v>
       </c>
       <c r="F96">
-        <v>1590.762</v>
+        <v>1607.685</v>
       </c>
       <c r="G96">
         <v>40.6</v>
@@ -9153,28 +9153,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M96">
-        <v>143.16858</v>
+        <v>144.69165</v>
       </c>
       <c r="N96">
-        <v>92.45475333333334</v>
+        <v>90.93168333333332</v>
       </c>
       <c r="O96">
-        <v>27.736426</v>
+        <v>27.279505</v>
       </c>
       <c r="P96">
-        <v>64.71832733333335</v>
+        <v>63.65217833333332</v>
       </c>
       <c r="Q96">
-        <v>69.92832733333334</v>
+        <v>68.86217833333332</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4792004902161833</v>
+        <v>0.5637075495898125</v>
       </c>
       <c r="T96">
-        <v>6.306505215081675</v>
+        <v>7.536185897688132</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.645775444118628</v>
+        <v>1.628451492075274</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.0880353774794906</v>
+        <v>0.08809872554601021</v>
       </c>
       <c r="C97">
-        <v>-118.2137491066401</v>
+        <v>-136.4268144725618</v>
       </c>
       <c r="D97">
-        <v>1448.87125089336</v>
+        <v>1447.581185527438</v>
       </c>
       <c r="E97">
-        <v>80.98500000000013</v>
+        <v>97.90800000000013</v>
       </c>
       <c r="F97">
-        <v>1607.685</v>
+        <v>1624.608</v>
       </c>
       <c r="G97">
         <v>40.6</v>
@@ -9235,28 +9235,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M97">
-        <v>144.69165</v>
+        <v>146.21472</v>
       </c>
       <c r="N97">
-        <v>90.93168333333332</v>
+        <v>89.40861333333334</v>
       </c>
       <c r="O97">
-        <v>27.279505</v>
+        <v>26.822584</v>
       </c>
       <c r="P97">
-        <v>63.65217833333332</v>
+        <v>62.58602933333334</v>
       </c>
       <c r="Q97">
-        <v>68.86217833333332</v>
+        <v>67.79602933333334</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5637075495898125</v>
+        <v>0.6904681386502565</v>
       </c>
       <c r="T97">
-        <v>7.536185897688132</v>
+        <v>9.38070692159782</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.628451492075274</v>
+        <v>1.61148845569949</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08809872554601021</v>
+        <v>0.08816207361252984</v>
       </c>
       <c r="C98">
-        <v>-136.4268144725615</v>
+        <v>-154.6375845508769</v>
       </c>
       <c r="D98">
-        <v>1447.581185527438</v>
+        <v>1446.293415449123</v>
       </c>
       <c r="E98">
-        <v>97.9079999999999</v>
+        <v>114.8309999999999</v>
       </c>
       <c r="F98">
-        <v>1624.608</v>
+        <v>1641.531</v>
       </c>
       <c r="G98">
         <v>40.6</v>
@@ -9317,28 +9317,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M98">
-        <v>146.21472</v>
+        <v>147.73779</v>
       </c>
       <c r="N98">
-        <v>89.40861333333334</v>
+        <v>87.88554333333335</v>
       </c>
       <c r="O98">
-        <v>26.822584</v>
+        <v>26.365663</v>
       </c>
       <c r="P98">
-        <v>62.58602933333334</v>
+        <v>61.51988033333335</v>
       </c>
       <c r="Q98">
-        <v>67.79602933333334</v>
+        <v>66.72988033333334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6904681386502547</v>
+        <v>0.9017357870843271</v>
       </c>
       <c r="T98">
-        <v>9.380706921597794</v>
+        <v>12.45490862811393</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.61148845569949</v>
+        <v>1.594875172651042</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08816207361252984</v>
+        <v>0.08822542167904945</v>
       </c>
       <c r="C99">
-        <v>-154.6375845508769</v>
+        <v>-172.8460654618134</v>
       </c>
       <c r="D99">
-        <v>1446.293415449123</v>
+        <v>1445.007934538187</v>
       </c>
       <c r="E99">
-        <v>114.8309999999999</v>
+        <v>131.7539999999999</v>
       </c>
       <c r="F99">
-        <v>1641.531</v>
+        <v>1658.454</v>
       </c>
       <c r="G99">
         <v>40.6</v>
@@ -9399,28 +9399,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M99">
-        <v>147.73779</v>
+        <v>149.26086</v>
       </c>
       <c r="N99">
-        <v>87.88554333333335</v>
+        <v>86.36247333333336</v>
       </c>
       <c r="O99">
-        <v>26.365663</v>
+        <v>25.90874200000001</v>
       </c>
       <c r="P99">
-        <v>61.51988033333335</v>
+        <v>60.45373133333335</v>
       </c>
       <c r="Q99">
-        <v>66.72988033333334</v>
+        <v>65.66373133333335</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9017357870843271</v>
+        <v>1.324271083952472</v>
       </c>
       <c r="T99">
-        <v>12.45490862811393</v>
+        <v>18.60331204114619</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.594875172651042</v>
+        <v>1.578600936195419</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08822542167904945</v>
+        <v>0.08828876974556907</v>
       </c>
       <c r="C100">
-        <v>-172.8460654618134</v>
+        <v>-191.0522633038593</v>
       </c>
       <c r="D100">
-        <v>1445.007934538187</v>
+        <v>1443.724736696141</v>
       </c>
       <c r="E100">
-        <v>131.7539999999999</v>
+        <v>148.6769999999999</v>
       </c>
       <c r="F100">
-        <v>1658.454</v>
+        <v>1675.377</v>
       </c>
       <c r="G100">
         <v>40.6</v>
@@ -9481,28 +9481,28 @@
         <v>235.6233333333333</v>
       </c>
       <c r="M100">
-        <v>149.26086</v>
+        <v>150.78393</v>
       </c>
       <c r="N100">
-        <v>86.36247333333336</v>
+        <v>84.83940333333334</v>
       </c>
       <c r="O100">
-        <v>25.90874200000001</v>
+        <v>25.451821</v>
       </c>
       <c r="P100">
-        <v>60.45373133333335</v>
+        <v>59.38758233333334</v>
       </c>
       <c r="Q100">
-        <v>65.66373133333335</v>
+        <v>64.59758233333334</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.324271083952472</v>
+        <v>2.591876974556905</v>
       </c>
       <c r="T100">
-        <v>18.60331204114619</v>
+        <v>37.04852228024298</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.578600936195419</v>
+        <v>1.562655472193445</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08828876974556907</v>
-      </c>
-      <c r="C101">
-        <v>-191.0522633038593</v>
-      </c>
-      <c r="D101">
-        <v>1443.724736696141</v>
-      </c>
-      <c r="E101">
-        <v>148.6769999999999</v>
-      </c>
-      <c r="F101">
-        <v>1675.377</v>
-      </c>
-      <c r="G101">
-        <v>40.6</v>
-      </c>
-      <c r="H101">
-        <v>165.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>240.8333333333333</v>
-      </c>
-      <c r="K101">
-        <v>5.21</v>
-      </c>
-      <c r="L101">
-        <v>235.6233333333333</v>
-      </c>
-      <c r="M101">
-        <v>150.78393</v>
-      </c>
-      <c r="N101">
-        <v>84.83940333333334</v>
-      </c>
-      <c r="O101">
-        <v>25.451821</v>
-      </c>
-      <c r="P101">
-        <v>59.38758233333334</v>
-      </c>
-      <c r="Q101">
-        <v>64.59758233333334</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.591876974556905</v>
-      </c>
-      <c r="T101">
-        <v>37.04852228024298</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.063</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.562655472193445</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
